--- a/documentation/Agile_Template_Completed_clean.xlsx
+++ b/documentation/Agile_Template_Completed_clean.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0ba97a91002e3819/Documents/AI-Career-companion-Agent/documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="212" documentId="11_21FE246E1D4E1EEB61B42CCB59C4DDD070F02EFE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B5645467-B52B-48A1-B0C6-CF0388A2E6F2}"/>
+  <xr:revisionPtr revIDLastSave="414" documentId="11_21FE246E1D4E1EEB61B42CCB59C4DDD070F02EFE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33E39911-A079-4FBB-916F-1615936C7D98}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="775" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="775" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Product Backlog" sheetId="1" r:id="rId1"/>
@@ -286,7 +286,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="306">
   <si>
     <t>SL #</t>
   </si>
@@ -1030,6 +1030,180 @@
   </si>
   <si>
     <t>As a student, I want job postings to be embedded and indexed so that the system can perform semantic search.</t>
+  </si>
+  <si>
+    <t>Sprint 4</t>
+  </si>
+  <si>
+    <t>US19</t>
+  </si>
+  <si>
+    <t>As a student, I want to add job and internship applications so that I can maintain a record of my application</t>
+  </si>
+  <si>
+    <t>Student Profile</t>
+  </si>
+  <si>
+    <t>US20</t>
+  </si>
+  <si>
+    <t>As a student, I want to view my saved applications so that I can monitor all my applications in one place.</t>
+  </si>
+  <si>
+    <t>Application Record</t>
+  </si>
+  <si>
+    <t>US21</t>
+  </si>
+  <si>
+    <t>As a student, I want to update my application status so that I can track recruitment progress</t>
+  </si>
+  <si>
+    <t>US22</t>
+  </si>
+  <si>
+    <t>As a student, I want to record important application dates and notes so that I can organize my recruitment activities.</t>
+  </si>
+  <si>
+    <t>SHOULD HAVE</t>
+  </si>
+  <si>
+    <t>Application Records</t>
+  </si>
+  <si>
+    <t>US23</t>
+  </si>
+  <si>
+    <t>As a student, I want to edit or remove an application record so that I can maintain accurate application information</t>
+  </si>
+  <si>
+    <t>Completed*</t>
+  </si>
+  <si>
+    <t>US24</t>
+  </si>
+  <si>
+    <t>As a student, I want to access application tracking from the existing Career Companion application so that I can manage my applications in one place.</t>
+  </si>
+  <si>
+    <t>Flask Application</t>
+  </si>
+  <si>
+    <t>T25</t>
+  </si>
+  <si>
+    <t>Review requirements and plan the Application Tracking Module</t>
+  </si>
+  <si>
+    <t>3 hours</t>
+  </si>
+  <si>
+    <t>T26</t>
+  </si>
+  <si>
+    <t>Design the application tracking interface</t>
+  </si>
+  <si>
+    <t>Design</t>
+  </si>
+  <si>
+    <t>T27</t>
+  </si>
+  <si>
+    <t>mplement adding and saving application records</t>
+  </si>
+  <si>
+    <t>Implement displaying saved application records</t>
+  </si>
+  <si>
+    <t>T28</t>
+  </si>
+  <si>
+    <t>T29</t>
+  </si>
+  <si>
+    <t>Implement updating application status</t>
+  </si>
+  <si>
+    <t>Implement application date and notes management</t>
+  </si>
+  <si>
+    <t>T30</t>
+  </si>
+  <si>
+    <t>T31</t>
+  </si>
+  <si>
+    <t>Implement editing and deleting application record</t>
+  </si>
+  <si>
+    <t>US25</t>
+  </si>
+  <si>
+    <t>T32</t>
+  </si>
+  <si>
+    <t>T33</t>
+  </si>
+  <si>
+    <t>Integrate the Application Tracking Module with the Flask application</t>
+  </si>
+  <si>
+    <t>Test application tracking workflows and resolve identified issues</t>
+  </si>
+  <si>
+    <t>Application tracking requirements needed to be finalized.</t>
+  </si>
+  <si>
+    <t>Reviewed the requirements and identified the application details to manage.</t>
+  </si>
+  <si>
+    <t>The application tracking interface needed to be designed</t>
+  </si>
+  <si>
+    <t>Designed the interface for displaying and managing application records.</t>
+  </si>
+  <si>
+    <t>Application details needed to be stored and retrieved.</t>
+  </si>
+  <si>
+    <t>Implemented the application record management functionality.</t>
+  </si>
+  <si>
+    <t>Users needed to monitor application progress</t>
+  </si>
+  <si>
+    <t>Implemented application status management</t>
+  </si>
+  <si>
+    <t>The module needed to work with the existing application.</t>
+  </si>
+  <si>
+    <t>Integrated the tracking module with the existing Flask application.</t>
+  </si>
+  <si>
+    <t>Application tracking workflows needed validation</t>
+  </si>
+  <si>
+    <t>Tested the supported workflows and corrected identified issues.</t>
+  </si>
+  <si>
+    <t>The final milestone needed review and demonstration preparation.</t>
+  </si>
+  <si>
+    <t>Reviewed the module and prepared the demonstration.</t>
+  </si>
+  <si>
+    <t>Validate application records and status updates using different test scenarios.</t>
+  </si>
+  <si>
+    <t>Making changes without testing the complete application workflow.</t>
+  </si>
+  <si>
+    <t>Testing individual features before testing the integrated application.</t>
+  </si>
+  <si>
+    <t>Reviewed and tested the Application Tracking Module, checked its integration, and addressed identified issues.</t>
   </si>
 </sst>
 </file>
@@ -1039,7 +1213,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-1009]d\-mmm\-yy;@"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -1100,12 +1274,6 @@
     <font>
       <sz val="10"/>
       <color rgb="FF00B050"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -1360,7 +1528,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1385,9 +1553,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1481,19 +1646,19 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1509,7 +1674,7 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1557,29 +1722,28 @@
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="15" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="13" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="13" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="12" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="15" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1903,28 +2067,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="37" t="s">
+      <c r="B1" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="38" t="s">
+      <c r="C1" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="38" t="s">
+      <c r="D1" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="38" t="s">
+      <c r="E1" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="F1" s="38" t="s">
+      <c r="F1" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="G1" s="38" t="s">
+      <c r="G1" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="H1" s="38" t="s">
+      <c r="H1" s="37" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1935,308 +2099,308 @@
       <c r="B2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="48" t="s">
+      <c r="C2" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="D2" s="49" t="s">
+      <c r="D2" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="E2" s="47" t="s">
+      <c r="E2" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="F2" s="47" t="s">
+      <c r="F2" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="G2" s="47" t="s">
+      <c r="G2" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="47" t="s">
+      <c r="H2" s="46" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="52" t="s">
+      <c r="A3" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="51" t="s">
+      <c r="B3" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="48" t="s">
+      <c r="C3" s="47" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="53" t="s">
+      <c r="D3" s="52" t="s">
         <v>35</v>
       </c>
-      <c r="E3" s="47" t="s">
+      <c r="E3" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="F3" s="47" t="s">
+      <c r="F3" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="G3" s="47" t="s">
+      <c r="G3" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="47" t="s">
+      <c r="H3" s="46" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="52" t="s">
+      <c r="A4" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="51" t="s">
+      <c r="B4" s="50" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="48" t="s">
+      <c r="C4" s="47" t="s">
         <v>38</v>
       </c>
-      <c r="D4" s="53" t="s">
+      <c r="D4" s="52" t="s">
         <v>39</v>
       </c>
-      <c r="E4" s="47" t="s">
+      <c r="E4" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="47" t="s">
+      <c r="F4" s="46" t="s">
         <v>40</v>
       </c>
-      <c r="G4" s="47" t="s">
+      <c r="G4" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="47" t="s">
+      <c r="H4" s="46" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="52" t="s">
+      <c r="A5" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="51" t="s">
+      <c r="B5" s="50" t="s">
         <v>41</v>
       </c>
-      <c r="C5" s="48" t="s">
+      <c r="C5" s="47" t="s">
         <v>42</v>
       </c>
-      <c r="D5" s="54" t="s">
+      <c r="D5" s="53" t="s">
         <v>43</v>
       </c>
-      <c r="E5" s="47" t="s">
+      <c r="E5" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="F5" s="47" t="s">
+      <c r="F5" s="46" t="s">
         <v>44</v>
       </c>
-      <c r="G5" s="47" t="s">
+      <c r="G5" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="47" t="s">
+      <c r="H5" s="46" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="52" t="s">
+      <c r="A6" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="51" t="s">
+      <c r="B6" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="48" t="s">
+      <c r="C6" s="47" t="s">
         <v>45</v>
       </c>
-      <c r="D6" s="54" t="s">
+      <c r="D6" s="53" t="s">
         <v>46</v>
       </c>
-      <c r="E6" s="47" t="s">
+      <c r="E6" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="F6" s="54" t="s">
+      <c r="F6" s="53" t="s">
         <v>47</v>
       </c>
-      <c r="G6" s="47" t="s">
+      <c r="G6" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="H6" s="47" t="s">
+      <c r="H6" s="46" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="41.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="51" t="s">
+      <c r="B7" s="50" t="s">
         <v>48</v>
       </c>
-      <c r="C7" s="48" t="s">
+      <c r="C7" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="D7" s="54" t="s">
+      <c r="D7" s="53" t="s">
         <v>50</v>
       </c>
-      <c r="E7" s="47" t="s">
+      <c r="E7" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="F7" s="47" t="s">
+      <c r="F7" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="G7" s="47" t="s">
+      <c r="G7" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="H7" s="47" t="s">
+      <c r="H7" s="46" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="51" t="s">
+      <c r="B8" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="48" t="s">
+      <c r="C8" s="47" t="s">
         <v>52</v>
       </c>
-      <c r="D8" s="54" t="s">
+      <c r="D8" s="53" t="s">
         <v>53</v>
       </c>
-      <c r="E8" s="47" t="s">
+      <c r="E8" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="F8" s="47" t="s">
+      <c r="F8" s="46" t="s">
         <v>54</v>
       </c>
-      <c r="G8" s="47" t="s">
+      <c r="G8" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="H8" s="47" t="s">
+      <c r="H8" s="46" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="52" t="s">
+      <c r="A9" s="51" t="s">
         <v>55</v>
       </c>
-      <c r="B9" s="51" t="s">
+      <c r="B9" s="50" t="s">
         <v>56</v>
       </c>
-      <c r="C9" s="48" t="s">
+      <c r="C9" s="47" t="s">
         <v>57</v>
       </c>
-      <c r="D9" s="54" t="s">
+      <c r="D9" s="53" t="s">
         <v>58</v>
       </c>
-      <c r="E9" s="47" t="s">
+      <c r="E9" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="F9" s="47" t="s">
+      <c r="F9" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="G9" s="47" t="s">
+      <c r="G9" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="H9" s="47" t="s">
+      <c r="H9" s="46" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="52" t="s">
+      <c r="A10" s="51" t="s">
         <v>60</v>
       </c>
-      <c r="B10" s="51" t="s">
+      <c r="B10" s="50" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="48" t="s">
+      <c r="C10" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="D10" s="54" t="s">
+      <c r="D10" s="53" t="s">
         <v>62</v>
       </c>
-      <c r="E10" s="47" t="s">
+      <c r="E10" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="F10" s="54" t="s">
+      <c r="F10" s="53" t="s">
         <v>63</v>
       </c>
-      <c r="G10" s="47" t="s">
+      <c r="G10" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="H10" s="47" t="s">
+      <c r="H10" s="46" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="55.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="47" t="s">
+      <c r="A11" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="47" t="s">
+      <c r="B11" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="48" t="s">
+      <c r="C11" s="47" t="s">
         <v>64</v>
       </c>
-      <c r="D11" s="54" t="s">
+      <c r="D11" s="53" t="s">
         <v>247</v>
       </c>
-      <c r="E11" s="47" t="s">
+      <c r="E11" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="F11" s="47" t="s">
+      <c r="F11" s="46" t="s">
         <v>65</v>
       </c>
-      <c r="G11" s="47" t="s">
+      <c r="G11" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="H11" s="47" t="s">
+      <c r="H11" s="46" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="47" t="s">
+      <c r="A12" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="47" t="s">
+      <c r="B12" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="48" t="s">
+      <c r="C12" s="47" t="s">
         <v>66</v>
       </c>
-      <c r="D12" s="54" t="s">
+      <c r="D12" s="53" t="s">
         <v>67</v>
       </c>
-      <c r="E12" s="47" t="s">
+      <c r="E12" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="F12" s="47" t="s">
+      <c r="F12" s="46" t="s">
         <v>68</v>
       </c>
-      <c r="G12" s="47" t="s">
+      <c r="G12" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="H12" s="47" t="s">
+      <c r="H12" s="46" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="47" t="s">
+      <c r="A13" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="47" t="s">
+      <c r="B13" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="48" t="s">
+      <c r="C13" s="47" t="s">
         <v>69</v>
       </c>
-      <c r="D13" s="54" t="s">
+      <c r="D13" s="53" t="s">
         <v>70</v>
       </c>
-      <c r="E13" s="47" t="s">
+      <c r="E13" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="F13" s="47" t="s">
+      <c r="F13" s="46" t="s">
         <v>71</v>
       </c>
-      <c r="G13" s="47" t="s">
+      <c r="G13" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="H13" s="47" t="s">
+      <c r="H13" s="46" t="s">
         <v>32</v>
       </c>
     </row>
@@ -2250,19 +2414,19 @@
       <c r="C14" t="s">
         <v>201</v>
       </c>
-      <c r="D14" s="54" t="s">
+      <c r="D14" s="53" t="s">
         <v>199</v>
       </c>
       <c r="E14" t="s">
         <v>30</v>
       </c>
-      <c r="F14" s="54" t="s">
+      <c r="F14" s="53" t="s">
         <v>200</v>
       </c>
-      <c r="G14" s="47" t="s">
+      <c r="G14" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="H14" s="47" t="s">
+      <c r="H14" s="46" t="s">
         <v>32</v>
       </c>
     </row>
@@ -2276,19 +2440,19 @@
       <c r="C15" t="s">
         <v>202</v>
       </c>
-      <c r="D15" s="54" t="s">
+      <c r="D15" s="53" t="s">
         <v>203</v>
       </c>
       <c r="E15" t="s">
         <v>30</v>
       </c>
-      <c r="F15" s="54" t="s">
+      <c r="F15" s="53" t="s">
         <v>200</v>
       </c>
-      <c r="G15" s="47" t="s">
+      <c r="G15" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="H15" s="47" t="s">
+      <c r="H15" s="46" t="s">
         <v>32</v>
       </c>
     </row>
@@ -2302,19 +2466,19 @@
       <c r="C16" t="s">
         <v>204</v>
       </c>
-      <c r="D16" s="72" t="s">
+      <c r="D16" t="s">
         <v>205</v>
       </c>
       <c r="E16" t="s">
         <v>30</v>
       </c>
-      <c r="F16" s="51" t="s">
+      <c r="F16" s="50" t="s">
         <v>206</v>
       </c>
-      <c r="G16" s="47" t="s">
+      <c r="G16" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="H16" s="47" t="s">
+      <c r="H16" s="46" t="s">
         <v>32</v>
       </c>
     </row>
@@ -2328,19 +2492,19 @@
       <c r="C17" t="s">
         <v>209</v>
       </c>
-      <c r="D17" s="51" t="s">
+      <c r="D17" s="50" t="s">
         <v>207</v>
       </c>
       <c r="E17" t="s">
         <v>30</v>
       </c>
-      <c r="F17" s="51" t="s">
+      <c r="F17" s="50" t="s">
         <v>208</v>
       </c>
-      <c r="G17" s="47" t="s">
+      <c r="G17" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="H17" s="47" t="s">
+      <c r="H17" s="46" t="s">
         <v>32</v>
       </c>
     </row>
@@ -2354,87 +2518,183 @@
       <c r="C18" t="s">
         <v>211</v>
       </c>
-      <c r="D18" s="54" t="s">
+      <c r="D18" s="53" t="s">
         <v>210</v>
       </c>
       <c r="E18" t="s">
         <v>30</v>
       </c>
-      <c r="F18" s="54" t="s">
+      <c r="F18" s="53" t="s">
         <v>212</v>
       </c>
-      <c r="G18" s="47" t="s">
+      <c r="G18" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="H18" s="47" t="s">
+      <c r="H18" s="46" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="15"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="15"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="15"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="6"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="15"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="6"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="6"/>
+    <row r="19" spans="1:8" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>248</v>
+      </c>
+      <c r="B19" t="s">
+        <v>248</v>
+      </c>
+      <c r="C19" t="s">
+        <v>249</v>
+      </c>
+      <c r="D19" s="53" t="s">
+        <v>250</v>
+      </c>
+      <c r="E19" t="s">
+        <v>30</v>
+      </c>
+      <c r="F19" t="s">
+        <v>251</v>
+      </c>
+      <c r="G19" t="s">
+        <v>10</v>
+      </c>
+      <c r="H19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>248</v>
+      </c>
+      <c r="B20" t="s">
+        <v>248</v>
+      </c>
+      <c r="C20" t="s">
+        <v>252</v>
+      </c>
+      <c r="D20" s="53" t="s">
+        <v>253</v>
+      </c>
+      <c r="E20" t="s">
+        <v>30</v>
+      </c>
+      <c r="F20" s="53" t="s">
+        <v>254</v>
+      </c>
+      <c r="G20" t="s">
+        <v>10</v>
+      </c>
+      <c r="H20" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="B21" t="s">
+        <v>248</v>
+      </c>
+      <c r="C21" t="s">
+        <v>255</v>
+      </c>
+      <c r="D21" s="53" t="s">
+        <v>256</v>
+      </c>
+      <c r="E21" t="s">
+        <v>30</v>
+      </c>
+      <c r="F21" s="53" t="s">
+        <v>254</v>
+      </c>
+      <c r="G21" t="s">
+        <v>10</v>
+      </c>
+      <c r="H21" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>248</v>
+      </c>
+      <c r="B22" t="s">
+        <v>248</v>
+      </c>
+      <c r="C22" t="s">
+        <v>257</v>
+      </c>
+      <c r="D22" s="53" t="s">
+        <v>258</v>
+      </c>
+      <c r="E22" t="s">
+        <v>259</v>
+      </c>
+      <c r="F22" s="53" t="s">
+        <v>260</v>
+      </c>
+      <c r="G22" t="s">
+        <v>10</v>
+      </c>
+      <c r="H22" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>248</v>
+      </c>
+      <c r="B23" t="s">
+        <v>248</v>
+      </c>
+      <c r="C23" t="s">
+        <v>261</v>
+      </c>
+      <c r="D23" s="53" t="s">
+        <v>262</v>
+      </c>
+      <c r="E23" t="s">
+        <v>259</v>
+      </c>
+      <c r="F23" s="53" t="s">
+        <v>260</v>
+      </c>
+      <c r="G23" t="s">
+        <v>10</v>
+      </c>
+      <c r="H23" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>248</v>
+      </c>
+      <c r="B24" t="s">
+        <v>248</v>
+      </c>
+      <c r="C24" t="s">
+        <v>264</v>
+      </c>
+      <c r="D24" s="53" t="s">
+        <v>265</v>
+      </c>
+      <c r="E24" t="s">
+        <v>30</v>
+      </c>
+      <c r="F24" t="s">
+        <v>266</v>
+      </c>
+      <c r="G24" t="s">
+        <v>10</v>
+      </c>
+      <c r="H24" s="50" t="s">
+        <v>263</v>
+      </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
-      <c r="C25" s="15"/>
-      <c r="D25" s="12"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="11"/>
       <c r="E25" s="6"/>
       <c r="F25" s="6"/>
       <c r="G25" s="6"/>
@@ -2443,8 +2703,8 @@
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
-      <c r="C26" s="15"/>
-      <c r="D26" s="14"/>
+      <c r="C26" s="14"/>
+      <c r="D26" s="13"/>
       <c r="E26" s="6"/>
       <c r="F26" s="6"/>
       <c r="G26" s="6"/>
@@ -2453,8 +2713,8 @@
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
-      <c r="C27" s="15"/>
-      <c r="D27" s="12"/>
+      <c r="C27" s="14"/>
+      <c r="D27" s="11"/>
       <c r="E27" s="6"/>
       <c r="F27" s="6"/>
       <c r="G27" s="6"/>
@@ -2463,8 +2723,8 @@
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
-      <c r="C28" s="15"/>
-      <c r="D28" s="12"/>
+      <c r="C28" s="14"/>
+      <c r="D28" s="11"/>
       <c r="E28" s="6"/>
       <c r="F28" s="6"/>
       <c r="G28" s="6"/>
@@ -2473,8 +2733,8 @@
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
-      <c r="C29" s="15"/>
-      <c r="D29" s="12"/>
+      <c r="C29" s="14"/>
+      <c r="D29" s="11"/>
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
       <c r="G29" s="6"/>
@@ -2483,8 +2743,8 @@
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
-      <c r="C30" s="15"/>
-      <c r="D30" s="14"/>
+      <c r="C30" s="14"/>
+      <c r="D30" s="13"/>
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
       <c r="G30" s="6"/>
@@ -2493,8 +2753,8 @@
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
-      <c r="C31" s="15"/>
-      <c r="D31" s="12"/>
+      <c r="C31" s="14"/>
+      <c r="D31" s="11"/>
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
       <c r="G31" s="6"/>
@@ -2503,8 +2763,8 @@
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
-      <c r="C32" s="15"/>
-      <c r="D32" s="12"/>
+      <c r="C32" s="14"/>
+      <c r="D32" s="11"/>
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
       <c r="G32" s="6"/>
@@ -2513,8 +2773,8 @@
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
-      <c r="C33" s="15"/>
-      <c r="D33" s="12"/>
+      <c r="C33" s="14"/>
+      <c r="D33" s="11"/>
       <c r="E33" s="6"/>
       <c r="F33" s="6"/>
       <c r="G33" s="6"/>
@@ -2523,8 +2783,8 @@
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
-      <c r="C34" s="15"/>
-      <c r="D34" s="14"/>
+      <c r="C34" s="14"/>
+      <c r="D34" s="13"/>
       <c r="E34" s="6"/>
       <c r="F34" s="6"/>
       <c r="G34" s="6"/>
@@ -2533,8 +2793,8 @@
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
-      <c r="C35" s="15"/>
-      <c r="D35" s="12"/>
+      <c r="C35" s="14"/>
+      <c r="D35" s="11"/>
       <c r="E35" s="6"/>
       <c r="F35" s="6"/>
       <c r="G35" s="6"/>
@@ -2543,8 +2803,8 @@
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
-      <c r="C36" s="15"/>
-      <c r="D36" s="12"/>
+      <c r="C36" s="14"/>
+      <c r="D36" s="11"/>
       <c r="E36" s="6"/>
       <c r="F36" s="6"/>
       <c r="G36" s="6"/>
@@ -2553,8 +2813,8 @@
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
-      <c r="C37" s="15"/>
-      <c r="D37" s="12"/>
+      <c r="C37" s="14"/>
+      <c r="D37" s="11"/>
       <c r="E37" s="6"/>
       <c r="F37" s="6"/>
       <c r="G37" s="6"/>
@@ -2563,8 +2823,8 @@
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
-      <c r="C38" s="15"/>
-      <c r="D38" s="14"/>
+      <c r="C38" s="14"/>
+      <c r="D38" s="13"/>
       <c r="E38" s="6"/>
       <c r="F38" s="6"/>
       <c r="G38" s="6"/>
@@ -2573,8 +2833,8 @@
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
-      <c r="C39" s="15"/>
-      <c r="D39" s="12"/>
+      <c r="C39" s="14"/>
+      <c r="D39" s="11"/>
       <c r="E39" s="6"/>
       <c r="F39" s="6"/>
       <c r="G39" s="6"/>
@@ -2583,8 +2843,8 @@
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
-      <c r="C40" s="15"/>
-      <c r="D40" s="12"/>
+      <c r="C40" s="14"/>
+      <c r="D40" s="11"/>
       <c r="E40" s="6"/>
       <c r="F40" s="6"/>
       <c r="G40" s="6"/>
@@ -2593,8 +2853,8 @@
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
-      <c r="C41" s="15"/>
-      <c r="D41" s="12"/>
+      <c r="C41" s="14"/>
+      <c r="D41" s="11"/>
       <c r="E41" s="6"/>
       <c r="F41" s="6"/>
       <c r="G41" s="6"/>
@@ -2603,8 +2863,8 @@
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
-      <c r="C42" s="15"/>
-      <c r="D42" s="14"/>
+      <c r="C42" s="14"/>
+      <c r="D42" s="13"/>
       <c r="E42" s="6"/>
       <c r="F42" s="6"/>
       <c r="G42" s="6"/>
@@ -2613,8 +2873,8 @@
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
-      <c r="C43" s="15"/>
-      <c r="D43" s="14"/>
+      <c r="C43" s="14"/>
+      <c r="D43" s="13"/>
       <c r="E43" s="6"/>
       <c r="F43" s="6"/>
       <c r="G43" s="6"/>
@@ -2623,8 +2883,8 @@
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
-      <c r="C44" s="15"/>
-      <c r="D44" s="12"/>
+      <c r="C44" s="14"/>
+      <c r="D44" s="11"/>
       <c r="E44" s="6"/>
       <c r="F44" s="6"/>
       <c r="G44" s="6"/>
@@ -2633,8 +2893,8 @@
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
-      <c r="C45" s="15"/>
-      <c r="D45" s="12"/>
+      <c r="C45" s="14"/>
+      <c r="D45" s="11"/>
       <c r="E45" s="6"/>
       <c r="F45" s="6"/>
       <c r="G45" s="6"/>
@@ -2643,8 +2903,8 @@
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
-      <c r="C46" s="15"/>
-      <c r="D46" s="12"/>
+      <c r="C46" s="14"/>
+      <c r="D46" s="11"/>
       <c r="E46" s="6"/>
       <c r="F46" s="6"/>
       <c r="G46" s="6"/>
@@ -2653,8 +2913,8 @@
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
-      <c r="C47" s="15"/>
-      <c r="D47" s="14"/>
+      <c r="C47" s="14"/>
+      <c r="D47" s="13"/>
       <c r="E47" s="6"/>
       <c r="F47" s="6"/>
       <c r="G47" s="6"/>
@@ -2663,8 +2923,8 @@
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
-      <c r="C48" s="15"/>
-      <c r="D48" s="14"/>
+      <c r="C48" s="14"/>
+      <c r="D48" s="13"/>
       <c r="E48" s="6"/>
       <c r="F48" s="6"/>
       <c r="G48" s="6"/>
@@ -2673,8 +2933,8 @@
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
-      <c r="C49" s="15"/>
-      <c r="D49" s="12"/>
+      <c r="C49" s="14"/>
+      <c r="D49" s="11"/>
       <c r="E49" s="6"/>
       <c r="F49" s="6"/>
       <c r="G49" s="6"/>
@@ -2683,8 +2943,8 @@
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
-      <c r="C50" s="15"/>
-      <c r="D50" s="12"/>
+      <c r="C50" s="14"/>
+      <c r="D50" s="11"/>
       <c r="E50" s="6"/>
       <c r="F50" s="6"/>
       <c r="G50" s="6"/>
@@ -2693,10 +2953,10 @@
   </sheetData>
   <phoneticPr fontId="10" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H50" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H18 H25:H50" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"1- Not Started, 2- In Progress, 3- Completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E13 E19:E50" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E13 E25:E50" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"MUST HAVE, SHOULD HAVE, COULD HAVE, WON'T HAVE"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2712,50 +2972,50 @@
   <dimension ref="A1:W106"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="10.199999999999999" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10" style="16" customWidth="1"/>
-    <col min="2" max="2" width="9.6640625" style="31" customWidth="1"/>
-    <col min="3" max="3" width="41.33203125" style="32" customWidth="1"/>
-    <col min="4" max="4" width="11.44140625" style="33" customWidth="1"/>
-    <col min="5" max="5" width="11.44140625" style="34" customWidth="1"/>
-    <col min="6" max="6" width="9.6640625" style="35" customWidth="1"/>
-    <col min="7" max="7" width="17" style="16" customWidth="1"/>
-    <col min="8" max="8" width="13.33203125" style="16" customWidth="1"/>
-    <col min="9" max="9" width="9.33203125" style="16" customWidth="1"/>
-    <col min="10" max="10" width="10.88671875" style="16" customWidth="1"/>
-    <col min="11" max="11" width="10.33203125" style="16" customWidth="1"/>
-    <col min="12" max="12" width="10.109375" style="16" customWidth="1"/>
-    <col min="13" max="13" width="9.109375" style="16" customWidth="1"/>
-    <col min="14" max="16384" width="9.109375" style="16"/>
+    <col min="1" max="1" width="10" style="15" customWidth="1"/>
+    <col min="2" max="2" width="9.6640625" style="30" customWidth="1"/>
+    <col min="3" max="3" width="41.33203125" style="31" customWidth="1"/>
+    <col min="4" max="4" width="11.44140625" style="32" customWidth="1"/>
+    <col min="5" max="5" width="11.44140625" style="33" customWidth="1"/>
+    <col min="6" max="6" width="9.6640625" style="34" customWidth="1"/>
+    <col min="7" max="7" width="17" style="15" customWidth="1"/>
+    <col min="8" max="8" width="13.33203125" style="15" customWidth="1"/>
+    <col min="9" max="9" width="9.33203125" style="15" customWidth="1"/>
+    <col min="10" max="10" width="10.88671875" style="15" customWidth="1"/>
+    <col min="11" max="11" width="10.33203125" style="15" customWidth="1"/>
+    <col min="12" max="12" width="10.109375" style="15" customWidth="1"/>
+    <col min="13" max="13" width="9.109375" style="15" customWidth="1"/>
+    <col min="14" max="16384" width="9.109375" style="15"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="42" t="s">
         <v>72</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44"/>
-      <c r="J1" s="44"/>
-      <c r="K1" s="44"/>
-      <c r="L1" s="44"/>
-      <c r="M1" s="44"/>
-      <c r="N1" s="44"/>
-      <c r="O1" s="44"/>
-      <c r="P1" s="44"/>
-      <c r="Q1" s="44"/>
-      <c r="R1" s="44"/>
-      <c r="S1" s="44"/>
-      <c r="T1" s="45"/>
-      <c r="U1" s="45"/>
-      <c r="V1" s="44"/>
-      <c r="W1" s="45"/>
-    </row>
-    <row r="2" spans="1:23" s="17" customFormat="1" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="43"/>
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="43"/>
+      <c r="N1" s="43"/>
+      <c r="O1" s="43"/>
+      <c r="P1" s="43"/>
+      <c r="Q1" s="43"/>
+      <c r="R1" s="43"/>
+      <c r="S1" s="43"/>
+      <c r="T1" s="44"/>
+      <c r="U1" s="44"/>
+      <c r="V1" s="43"/>
+      <c r="W1" s="44"/>
+    </row>
+    <row r="2" spans="1:23" s="16" customFormat="1" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="69" t="s">
         <v>22</v>
       </c>
@@ -2780,53 +3040,53 @@
       <c r="H2" s="65" t="s">
         <v>27</v>
       </c>
-      <c r="I2" s="40" t="s">
+      <c r="I2" s="39" t="s">
         <v>79</v>
       </c>
-      <c r="J2" s="41" t="s">
+      <c r="J2" s="40" t="s">
         <v>80</v>
       </c>
-      <c r="K2" s="41" t="s">
+      <c r="K2" s="40" t="s">
         <v>81</v>
       </c>
-      <c r="L2" s="41" t="s">
+      <c r="L2" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="M2" s="41" t="s">
+      <c r="M2" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="N2" s="41" t="s">
+      <c r="N2" s="40" t="s">
         <v>84</v>
       </c>
-      <c r="O2" s="41" t="s">
+      <c r="O2" s="40" t="s">
         <v>85</v>
       </c>
-      <c r="P2" s="41" t="s">
+      <c r="P2" s="40" t="s">
         <v>86</v>
       </c>
-      <c r="Q2" s="41" t="s">
+      <c r="Q2" s="40" t="s">
         <v>87</v>
       </c>
-      <c r="R2" s="41" t="s">
+      <c r="R2" s="40" t="s">
         <v>88</v>
       </c>
-      <c r="S2" s="41" t="s">
+      <c r="S2" s="40" t="s">
         <v>89</v>
       </c>
-      <c r="T2" s="41" t="s">
+      <c r="T2" s="40" t="s">
         <v>90</v>
       </c>
-      <c r="U2" s="41" t="s">
+      <c r="U2" s="40" t="s">
         <v>91</v>
       </c>
-      <c r="V2" s="41" t="s">
+      <c r="V2" s="40" t="s">
         <v>92</v>
       </c>
-      <c r="W2" s="41" t="s">
+      <c r="W2" s="40" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="3" spans="1:23" s="17" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:23" s="16" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="70"/>
       <c r="B3" s="68"/>
       <c r="C3" s="66"/>
@@ -2835,68 +3095,68 @@
       <c r="F3" s="66"/>
       <c r="G3" s="66"/>
       <c r="H3" s="66"/>
-      <c r="I3" s="46">
+      <c r="I3" s="45">
         <f t="shared" ref="I3:W3" si="0">SUM(I5:I802)</f>
         <v>0</v>
       </c>
-      <c r="J3" s="46">
+      <c r="J3" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K3" s="46">
+      <c r="K3" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L3" s="46">
+      <c r="L3" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="M3" s="46">
+      <c r="M3" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N3" s="46">
+      <c r="N3" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O3" s="46">
+      <c r="O3" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P3" s="46">
+      <c r="P3" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q3" s="46">
+      <c r="Q3" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R3" s="46">
+      <c r="R3" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="S3" s="46">
+      <c r="S3" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="T3" s="46">
+      <c r="T3" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U3" s="46">
+      <c r="U3" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V3" s="46">
+      <c r="V3" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="W3" s="46">
+      <c r="W3" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:23" s="17" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:23" s="16" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="62" t="s">
         <v>94</v>
       </c>
@@ -2924,2143 +3184,2297 @@
       <c r="W4" s="64"/>
     </row>
     <row r="5" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="50" t="s">
+      <c r="A5" s="49" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="21" t="s">
         <v>95</v>
       </c>
-      <c r="C5" s="56" t="s">
+      <c r="C5" s="55" t="s">
         <v>96</v>
       </c>
-      <c r="D5" s="42">
+      <c r="D5" s="41">
         <v>46260</v>
       </c>
-      <c r="E5" s="42">
+      <c r="E5" s="41">
         <v>46260</v>
       </c>
-      <c r="F5" s="56" t="s">
+      <c r="F5" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="G5" s="55" t="s">
+      <c r="G5" s="54" t="s">
         <v>97</v>
       </c>
-      <c r="H5" s="55" t="s">
+      <c r="H5" s="54" t="s">
         <v>98</v>
       </c>
-      <c r="I5" s="55" t="s">
+      <c r="I5" s="54" t="s">
         <v>99</v>
       </c>
-      <c r="J5" s="56" t="s">
+      <c r="J5" s="55" t="s">
         <v>100</v>
       </c>
-      <c r="K5" s="21"/>
-      <c r="L5" s="21"/>
-      <c r="M5" s="21"/>
-      <c r="N5" s="21"/>
-      <c r="O5" s="23"/>
-      <c r="P5" s="23"/>
-      <c r="Q5" s="23"/>
-      <c r="R5" s="23"/>
-      <c r="S5" s="23"/>
-      <c r="T5" s="21"/>
-      <c r="U5" s="21"/>
-      <c r="V5" s="21"/>
-      <c r="W5" s="21"/>
+      <c r="K5" s="20"/>
+      <c r="L5" s="20"/>
+      <c r="M5" s="20"/>
+      <c r="N5" s="20"/>
+      <c r="O5" s="22"/>
+      <c r="P5" s="22"/>
+      <c r="Q5" s="22"/>
+      <c r="R5" s="22"/>
+      <c r="S5" s="22"/>
+      <c r="T5" s="20"/>
+      <c r="U5" s="20"/>
+      <c r="V5" s="20"/>
+      <c r="W5" s="20"/>
     </row>
     <row r="6" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="50" t="s">
+      <c r="A6" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="C6" s="55" t="s">
+      <c r="C6" s="54" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="57">
+      <c r="D6" s="56">
         <v>46261</v>
       </c>
-      <c r="E6" s="57">
+      <c r="E6" s="56">
         <v>46261</v>
       </c>
-      <c r="F6" s="56" t="s">
+      <c r="F6" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="G6" s="55" t="s">
+      <c r="G6" s="54" t="s">
         <v>103</v>
       </c>
-      <c r="H6" s="55" t="s">
+      <c r="H6" s="54" t="s">
         <v>98</v>
       </c>
-      <c r="I6" s="55" t="s">
+      <c r="I6" s="54" t="s">
         <v>104</v>
       </c>
-      <c r="J6" s="21"/>
-      <c r="K6" s="56" t="s">
+      <c r="J6" s="20"/>
+      <c r="K6" s="55" t="s">
         <v>105</v>
       </c>
-      <c r="L6" s="21"/>
-      <c r="M6" s="21"/>
-      <c r="N6" s="21"/>
-      <c r="O6" s="23"/>
-      <c r="P6" s="23"/>
-      <c r="Q6" s="23"/>
-      <c r="R6" s="23"/>
-      <c r="S6" s="23"/>
-      <c r="T6" s="23"/>
-      <c r="U6" s="23"/>
-      <c r="V6" s="23"/>
-      <c r="W6" s="23"/>
+      <c r="L6" s="20"/>
+      <c r="M6" s="20"/>
+      <c r="N6" s="20"/>
+      <c r="O6" s="22"/>
+      <c r="P6" s="22"/>
+      <c r="Q6" s="22"/>
+      <c r="R6" s="22"/>
+      <c r="S6" s="22"/>
+      <c r="T6" s="22"/>
+      <c r="U6" s="22"/>
+      <c r="V6" s="22"/>
+      <c r="W6" s="22"/>
     </row>
     <row r="7" spans="1:23" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="50" t="s">
+      <c r="A7" s="49" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="C7" s="56" t="s">
+      <c r="C7" s="55" t="s">
         <v>107</v>
       </c>
-      <c r="D7" s="57">
+      <c r="D7" s="56">
         <v>46261</v>
       </c>
-      <c r="E7" s="57">
+      <c r="E7" s="56">
         <v>46261</v>
       </c>
-      <c r="F7" s="56" t="s">
+      <c r="F7" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="55" t="s">
+      <c r="G7" s="54" t="s">
         <v>103</v>
       </c>
-      <c r="H7" s="20" t="s">
+      <c r="H7" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="I7" s="55" t="s">
+      <c r="I7" s="54" t="s">
         <v>108</v>
       </c>
-      <c r="J7" s="23"/>
-      <c r="K7" s="23"/>
-      <c r="L7" s="56" t="s">
+      <c r="J7" s="22"/>
+      <c r="K7" s="22"/>
+      <c r="L7" s="55" t="s">
         <v>109</v>
       </c>
-      <c r="M7" s="23"/>
-      <c r="N7" s="23"/>
-      <c r="O7" s="23"/>
-      <c r="P7" s="23"/>
-      <c r="Q7" s="23"/>
-      <c r="R7" s="23"/>
-      <c r="S7" s="23"/>
-      <c r="T7" s="23"/>
-      <c r="U7" s="23"/>
-      <c r="V7" s="23"/>
-      <c r="W7" s="23"/>
+      <c r="M7" s="22"/>
+      <c r="N7" s="22"/>
+      <c r="O7" s="22"/>
+      <c r="P7" s="22"/>
+      <c r="Q7" s="22"/>
+      <c r="R7" s="22"/>
+      <c r="S7" s="22"/>
+      <c r="T7" s="22"/>
+      <c r="U7" s="22"/>
+      <c r="V7" s="22"/>
+      <c r="W7" s="22"/>
     </row>
     <row r="8" spans="1:23" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="50" t="s">
+      <c r="A8" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="21" t="s">
         <v>110</v>
       </c>
-      <c r="C8" s="55" t="s">
+      <c r="C8" s="54" t="s">
         <v>111</v>
       </c>
-      <c r="D8" s="57">
+      <c r="D8" s="56">
         <v>46263</v>
       </c>
-      <c r="E8" s="57">
+      <c r="E8" s="56">
         <v>46263</v>
       </c>
-      <c r="F8" s="56" t="s">
+      <c r="F8" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="55" t="s">
+      <c r="G8" s="54" t="s">
         <v>103</v>
       </c>
-      <c r="H8" s="20" t="s">
+      <c r="H8" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="I8" s="55" t="s">
+      <c r="I8" s="54" t="s">
         <v>112</v>
       </c>
-      <c r="J8" s="21"/>
-      <c r="K8" s="21"/>
-      <c r="L8" s="21"/>
-      <c r="M8" s="56" t="s">
+      <c r="J8" s="20"/>
+      <c r="K8" s="20"/>
+      <c r="L8" s="20"/>
+      <c r="M8" s="55" t="s">
         <v>113</v>
       </c>
-      <c r="N8" s="21"/>
-      <c r="O8" s="23"/>
-      <c r="P8" s="23"/>
-      <c r="Q8" s="23"/>
-      <c r="R8" s="23"/>
-      <c r="S8" s="23"/>
-      <c r="T8" s="23"/>
-      <c r="U8" s="23"/>
-      <c r="V8" s="23"/>
-      <c r="W8" s="23"/>
+      <c r="N8" s="20"/>
+      <c r="O8" s="22"/>
+      <c r="P8" s="22"/>
+      <c r="Q8" s="22"/>
+      <c r="R8" s="22"/>
+      <c r="S8" s="22"/>
+      <c r="T8" s="22"/>
+      <c r="U8" s="22"/>
+      <c r="V8" s="22"/>
+      <c r="W8" s="22"/>
     </row>
     <row r="9" spans="1:23" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="50" t="s">
+      <c r="A9" s="49" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="22" t="s">
+      <c r="B9" s="21" t="s">
         <v>114</v>
       </c>
-      <c r="C9" s="55" t="s">
+      <c r="C9" s="54" t="s">
         <v>115</v>
       </c>
-      <c r="D9" s="57">
+      <c r="D9" s="56">
         <v>46264</v>
       </c>
-      <c r="E9" s="42">
+      <c r="E9" s="41">
         <v>46264</v>
       </c>
-      <c r="F9" s="56" t="s">
+      <c r="F9" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="G9" s="55" t="s">
+      <c r="G9" s="54" t="s">
         <v>103</v>
       </c>
-      <c r="H9" s="20" t="s">
+      <c r="H9" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="I9" s="55" t="s">
+      <c r="I9" s="54" t="s">
         <v>104</v>
       </c>
-      <c r="J9" s="21"/>
-      <c r="K9" s="21"/>
-      <c r="L9" s="21"/>
-      <c r="M9" s="21"/>
-      <c r="N9" s="56" t="s">
+      <c r="J9" s="20"/>
+      <c r="K9" s="20"/>
+      <c r="L9" s="20"/>
+      <c r="M9" s="20"/>
+      <c r="N9" s="55" t="s">
         <v>116</v>
       </c>
-      <c r="O9" s="23"/>
-      <c r="P9" s="23"/>
-      <c r="Q9" s="23"/>
-      <c r="R9" s="23"/>
-      <c r="S9" s="23"/>
-      <c r="T9" s="23"/>
-      <c r="U9" s="23"/>
-      <c r="V9" s="23"/>
-      <c r="W9" s="23"/>
+      <c r="O9" s="22"/>
+      <c r="P9" s="22"/>
+      <c r="Q9" s="22"/>
+      <c r="R9" s="22"/>
+      <c r="S9" s="22"/>
+      <c r="T9" s="22"/>
+      <c r="U9" s="22"/>
+      <c r="V9" s="22"/>
+      <c r="W9" s="22"/>
     </row>
     <row r="10" spans="1:23" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="50" t="s">
+      <c r="A10" s="49" t="s">
         <v>49</v>
       </c>
-      <c r="B10" s="42" t="s">
+      <c r="B10" s="41" t="s">
         <v>117</v>
       </c>
-      <c r="C10" s="55" t="s">
+      <c r="C10" s="54" t="s">
         <v>118</v>
       </c>
-      <c r="D10" s="58">
+      <c r="D10" s="57">
         <v>46265</v>
       </c>
-      <c r="E10" s="34">
+      <c r="E10" s="33">
         <v>46265</v>
       </c>
-      <c r="F10" s="56" t="s">
+      <c r="F10" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="G10" s="55" t="s">
+      <c r="G10" s="54" t="s">
         <v>103</v>
       </c>
-      <c r="H10" s="20" t="s">
+      <c r="H10" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="I10" s="55" t="s">
+      <c r="I10" s="54" t="s">
         <v>108</v>
       </c>
-      <c r="J10" s="21"/>
-      <c r="K10" s="21"/>
-      <c r="L10" s="21"/>
-      <c r="M10" s="23"/>
-      <c r="N10" s="23"/>
-      <c r="O10" s="56" t="s">
+      <c r="J10" s="20"/>
+      <c r="K10" s="20"/>
+      <c r="L10" s="20"/>
+      <c r="M10" s="22"/>
+      <c r="N10" s="22"/>
+      <c r="O10" s="55" t="s">
         <v>119</v>
       </c>
-      <c r="P10" s="23"/>
-      <c r="Q10" s="23"/>
-      <c r="R10" s="23"/>
-      <c r="S10" s="23"/>
-      <c r="T10" s="23"/>
-      <c r="U10" s="23"/>
-      <c r="V10" s="23"/>
-      <c r="W10" s="23"/>
+      <c r="P10" s="22"/>
+      <c r="Q10" s="22"/>
+      <c r="R10" s="22"/>
+      <c r="S10" s="22"/>
+      <c r="T10" s="22"/>
+      <c r="U10" s="22"/>
+      <c r="V10" s="22"/>
+      <c r="W10" s="22"/>
     </row>
     <row r="11" spans="1:23" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="50" t="s">
+      <c r="A11" s="49" t="s">
         <v>52</v>
       </c>
-      <c r="B11" s="42" t="s">
+      <c r="B11" s="41" t="s">
         <v>120</v>
       </c>
-      <c r="C11" s="56" t="s">
+      <c r="C11" s="55" t="s">
         <v>121</v>
       </c>
-      <c r="D11" s="57">
+      <c r="D11" s="56">
         <v>46266</v>
       </c>
-      <c r="E11" s="57">
+      <c r="E11" s="56">
         <v>46267</v>
       </c>
-      <c r="F11" s="56" t="s">
+      <c r="F11" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="G11" s="55" t="s">
+      <c r="G11" s="54" t="s">
         <v>122</v>
       </c>
-      <c r="H11" s="20" t="s">
+      <c r="H11" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="I11" s="55" t="s">
+      <c r="I11" s="54" t="s">
         <v>123</v>
       </c>
-      <c r="J11" s="21"/>
-      <c r="K11" s="21"/>
-      <c r="L11" s="21"/>
-      <c r="M11" s="23"/>
-      <c r="N11" s="23"/>
-      <c r="O11" s="23"/>
-      <c r="P11" s="56" t="s">
+      <c r="J11" s="20"/>
+      <c r="K11" s="20"/>
+      <c r="L11" s="20"/>
+      <c r="M11" s="22"/>
+      <c r="N11" s="22"/>
+      <c r="O11" s="22"/>
+      <c r="P11" s="55" t="s">
         <v>124</v>
       </c>
-      <c r="Q11" s="23"/>
-      <c r="R11" s="23"/>
-      <c r="S11" s="23"/>
-      <c r="T11" s="23"/>
-      <c r="U11" s="23"/>
-      <c r="V11" s="23"/>
-      <c r="W11" s="23"/>
+      <c r="Q11" s="22"/>
+      <c r="R11" s="22"/>
+      <c r="S11" s="22"/>
+      <c r="T11" s="22"/>
+      <c r="U11" s="22"/>
+      <c r="V11" s="22"/>
+      <c r="W11" s="22"/>
     </row>
     <row r="12" spans="1:23" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="50" t="s">
+      <c r="A12" s="49" t="s">
         <v>125</v>
       </c>
-      <c r="B12" s="42" t="s">
+      <c r="B12" s="41" t="s">
         <v>126</v>
       </c>
-      <c r="C12" s="56" t="s">
+      <c r="C12" s="55" t="s">
         <v>127</v>
       </c>
-      <c r="D12" s="58">
+      <c r="D12" s="57">
         <v>46269</v>
       </c>
-      <c r="E12" s="57">
+      <c r="E12" s="56">
         <v>46269</v>
       </c>
-      <c r="F12" s="56" t="s">
+      <c r="F12" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="G12" s="55" t="s">
+      <c r="G12" s="54" t="s">
         <v>10</v>
       </c>
-      <c r="H12" s="55" t="s">
+      <c r="H12" s="54" t="s">
         <v>98</v>
       </c>
-      <c r="I12" s="55" t="s">
+      <c r="I12" s="54" t="s">
         <v>104</v>
       </c>
-      <c r="J12" s="56" t="s">
+      <c r="J12" s="55" t="s">
         <v>128</v>
       </c>
-      <c r="K12" s="23"/>
-      <c r="L12" s="23"/>
-      <c r="M12" s="23"/>
-      <c r="N12" s="23"/>
-      <c r="O12" s="23"/>
-      <c r="P12" s="23"/>
-      <c r="Q12" s="23"/>
-      <c r="R12" s="23"/>
-      <c r="S12" s="23"/>
-      <c r="T12" s="23"/>
-      <c r="U12" s="23"/>
-      <c r="V12" s="23"/>
-      <c r="W12" s="23"/>
+      <c r="K12" s="22"/>
+      <c r="L12" s="22"/>
+      <c r="M12" s="22"/>
+      <c r="N12" s="22"/>
+      <c r="O12" s="22"/>
+      <c r="P12" s="22"/>
+      <c r="Q12" s="22"/>
+      <c r="R12" s="22"/>
+      <c r="S12" s="22"/>
+      <c r="T12" s="22"/>
+      <c r="U12" s="22"/>
+      <c r="V12" s="22"/>
+      <c r="W12" s="22"/>
     </row>
     <row r="13" spans="1:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="50" t="s">
+      <c r="A13" s="49" t="s">
         <v>129</v>
       </c>
-      <c r="B13" s="42" t="s">
+      <c r="B13" s="41" t="s">
         <v>130</v>
       </c>
-      <c r="C13" s="56" t="s">
+      <c r="C13" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="D13" s="57">
+      <c r="D13" s="56">
         <v>46270</v>
       </c>
-      <c r="E13" s="57">
+      <c r="E13" s="56">
         <v>46270</v>
       </c>
-      <c r="F13" s="56" t="s">
+      <c r="F13" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="G13" s="55" t="s">
+      <c r="G13" s="54" t="s">
         <v>103</v>
       </c>
-      <c r="H13" s="55" t="s">
+      <c r="H13" s="54" t="s">
         <v>98</v>
       </c>
-      <c r="I13" s="55" t="s">
+      <c r="I13" s="54" t="s">
         <v>112</v>
       </c>
-      <c r="J13" s="21"/>
-      <c r="K13" s="56" t="s">
+      <c r="J13" s="20"/>
+      <c r="K13" s="55" t="s">
         <v>132</v>
       </c>
-      <c r="L13" s="21"/>
-      <c r="M13" s="23"/>
-      <c r="N13" s="23"/>
-      <c r="O13" s="23"/>
-      <c r="P13" s="23"/>
-      <c r="Q13" s="23"/>
-      <c r="R13" s="23"/>
-      <c r="S13" s="23"/>
-      <c r="T13" s="23"/>
-      <c r="U13" s="23"/>
-      <c r="V13" s="23"/>
-      <c r="W13" s="23"/>
+      <c r="L13" s="20"/>
+      <c r="M13" s="22"/>
+      <c r="N13" s="22"/>
+      <c r="O13" s="22"/>
+      <c r="P13" s="22"/>
+      <c r="Q13" s="22"/>
+      <c r="R13" s="22"/>
+      <c r="S13" s="22"/>
+      <c r="T13" s="22"/>
+      <c r="U13" s="22"/>
+      <c r="V13" s="22"/>
+      <c r="W13" s="22"/>
     </row>
     <row r="14" spans="1:23" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="50" t="s">
+      <c r="A14" s="49" t="s">
         <v>129</v>
       </c>
-      <c r="B14" s="42" t="s">
+      <c r="B14" s="41" t="s">
         <v>133</v>
       </c>
-      <c r="C14" s="56" t="s">
+      <c r="C14" s="55" t="s">
         <v>134</v>
       </c>
-      <c r="D14" s="57">
+      <c r="D14" s="56">
         <v>46271</v>
       </c>
-      <c r="E14" s="57">
+      <c r="E14" s="56">
         <v>46271</v>
       </c>
-      <c r="F14" s="56" t="s">
+      <c r="F14" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="G14" s="55" t="s">
+      <c r="G14" s="54" t="s">
         <v>103</v>
       </c>
-      <c r="H14" s="55" t="s">
+      <c r="H14" s="54" t="s">
         <v>98</v>
       </c>
-      <c r="I14" s="55" t="s">
+      <c r="I14" s="54" t="s">
         <v>112</v>
       </c>
-      <c r="J14" s="21"/>
-      <c r="K14" s="21"/>
-      <c r="L14" s="56" t="s">
+      <c r="J14" s="20"/>
+      <c r="K14" s="20"/>
+      <c r="L14" s="55" t="s">
         <v>135</v>
       </c>
-      <c r="M14" s="23"/>
-      <c r="N14" s="23"/>
-      <c r="O14" s="23"/>
-      <c r="P14" s="23"/>
-      <c r="Q14" s="23"/>
-      <c r="R14" s="23"/>
-      <c r="S14" s="23"/>
-      <c r="T14" s="23"/>
-      <c r="U14" s="23"/>
-      <c r="V14" s="23"/>
-      <c r="W14" s="23"/>
+      <c r="M14" s="22"/>
+      <c r="N14" s="22"/>
+      <c r="O14" s="22"/>
+      <c r="P14" s="22"/>
+      <c r="Q14" s="22"/>
+      <c r="R14" s="22"/>
+      <c r="S14" s="22"/>
+      <c r="T14" s="22"/>
+      <c r="U14" s="22"/>
+      <c r="V14" s="22"/>
+      <c r="W14" s="22"/>
     </row>
     <row r="15" spans="1:23" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="55" t="s">
+      <c r="A15" s="54" t="s">
         <v>129</v>
       </c>
-      <c r="B15" s="55" t="s">
+      <c r="B15" s="54" t="s">
         <v>136</v>
       </c>
-      <c r="C15" s="56" t="s">
+      <c r="C15" s="55" t="s">
         <v>137</v>
       </c>
-      <c r="D15" s="57">
+      <c r="D15" s="56">
         <v>46272</v>
       </c>
-      <c r="E15" s="57">
+      <c r="E15" s="56">
         <v>46272</v>
       </c>
-      <c r="F15" s="56" t="s">
+      <c r="F15" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="G15" s="55" t="s">
+      <c r="G15" s="54" t="s">
         <v>103</v>
       </c>
-      <c r="H15" s="20" t="s">
+      <c r="H15" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="I15" s="55" t="s">
+      <c r="I15" s="54" t="s">
         <v>104</v>
       </c>
-      <c r="J15" s="21"/>
-      <c r="K15" s="21"/>
-      <c r="L15" s="21"/>
-      <c r="M15" s="56" t="s">
+      <c r="J15" s="20"/>
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+      <c r="M15" s="55" t="s">
         <v>138</v>
       </c>
-      <c r="N15" s="23"/>
-      <c r="O15" s="23"/>
-      <c r="P15" s="23"/>
-      <c r="Q15" s="23"/>
-      <c r="R15" s="23"/>
-      <c r="S15" s="23"/>
-      <c r="T15" s="23"/>
-      <c r="U15" s="23"/>
-      <c r="V15" s="23"/>
-      <c r="W15" s="23"/>
+      <c r="N15" s="22"/>
+      <c r="O15" s="22"/>
+      <c r="P15" s="22"/>
+      <c r="Q15" s="22"/>
+      <c r="R15" s="22"/>
+      <c r="S15" s="22"/>
+      <c r="T15" s="22"/>
+      <c r="U15" s="22"/>
+      <c r="V15" s="22"/>
+      <c r="W15" s="22"/>
     </row>
     <row r="16" spans="1:23" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="55" t="s">
+      <c r="A16" s="54" t="s">
         <v>129</v>
       </c>
-      <c r="B16" s="55" t="s">
+      <c r="B16" s="54" t="s">
         <v>139</v>
       </c>
-      <c r="C16" s="56" t="s">
+      <c r="C16" s="55" t="s">
         <v>140</v>
       </c>
-      <c r="D16" s="57">
+      <c r="D16" s="56">
         <v>46273</v>
       </c>
-      <c r="E16" s="57">
+      <c r="E16" s="56">
         <v>46273</v>
       </c>
-      <c r="F16" s="56" t="s">
+      <c r="F16" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="G16" s="55" t="s">
+      <c r="G16" s="54" t="s">
         <v>103</v>
       </c>
-      <c r="H16" s="55" t="s">
+      <c r="H16" s="54" t="s">
         <v>141</v>
       </c>
-      <c r="I16" s="55" t="s">
+      <c r="I16" s="54" t="s">
         <v>112</v>
       </c>
-      <c r="J16" s="21"/>
-      <c r="K16" s="21"/>
-      <c r="L16" s="21"/>
-      <c r="M16" s="23"/>
-      <c r="N16" s="56" t="s">
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+      <c r="M16" s="22"/>
+      <c r="N16" s="55" t="s">
         <v>142</v>
       </c>
-      <c r="O16" s="23"/>
-      <c r="P16" s="23"/>
-      <c r="Q16" s="23"/>
-      <c r="R16" s="23"/>
-      <c r="S16" s="23"/>
-      <c r="T16" s="23"/>
-      <c r="U16" s="23"/>
-      <c r="V16" s="23"/>
-      <c r="W16" s="23"/>
+      <c r="O16" s="22"/>
+      <c r="P16" s="22"/>
+      <c r="Q16" s="22"/>
+      <c r="R16" s="22"/>
+      <c r="S16" s="22"/>
+      <c r="T16" s="22"/>
+      <c r="U16" s="22"/>
+      <c r="V16" s="22"/>
+      <c r="W16" s="22"/>
     </row>
     <row r="17" spans="1:23" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="55" t="s">
+      <c r="A17" s="54" t="s">
         <v>64</v>
       </c>
-      <c r="B17" s="55" t="s">
+      <c r="B17" s="54" t="s">
         <v>143</v>
       </c>
-      <c r="C17" s="56" t="s">
+      <c r="C17" s="55" t="s">
         <v>144</v>
       </c>
-      <c r="D17" s="57">
+      <c r="D17" s="56">
         <v>46274</v>
       </c>
-      <c r="E17" s="57">
+      <c r="E17" s="56">
         <v>46274</v>
       </c>
-      <c r="F17" s="56" t="s">
+      <c r="F17" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="G17" s="55" t="s">
+      <c r="G17" s="54" t="s">
         <v>103</v>
       </c>
-      <c r="H17" s="55" t="s">
+      <c r="H17" s="54" t="s">
         <v>141</v>
       </c>
-      <c r="I17" s="55" t="s">
+      <c r="I17" s="54" t="s">
         <v>104</v>
       </c>
-      <c r="J17" s="21"/>
-      <c r="K17" s="21"/>
-      <c r="L17" s="21"/>
-      <c r="M17" s="23"/>
-      <c r="N17" s="23"/>
-      <c r="O17" s="56" t="s">
+      <c r="J17" s="20"/>
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+      <c r="M17" s="22"/>
+      <c r="N17" s="22"/>
+      <c r="O17" s="55" t="s">
         <v>145</v>
       </c>
-      <c r="P17" s="23"/>
-      <c r="Q17" s="23"/>
-      <c r="R17" s="23"/>
-      <c r="S17" s="23"/>
-      <c r="T17" s="23"/>
-      <c r="U17" s="23"/>
-      <c r="V17" s="23"/>
-      <c r="W17" s="23"/>
+      <c r="P17" s="22"/>
+      <c r="Q17" s="22"/>
+      <c r="R17" s="22"/>
+      <c r="S17" s="22"/>
+      <c r="T17" s="22"/>
+      <c r="U17" s="22"/>
+      <c r="V17" s="22"/>
+      <c r="W17" s="22"/>
     </row>
     <row r="18" spans="1:23" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="55" t="s">
+      <c r="A18" s="54" t="s">
         <v>66</v>
       </c>
-      <c r="B18" s="55" t="s">
+      <c r="B18" s="54" t="s">
         <v>146</v>
       </c>
-      <c r="C18" s="56" t="s">
+      <c r="C18" s="55" t="s">
         <v>147</v>
       </c>
-      <c r="D18" s="57">
+      <c r="D18" s="56">
         <v>46275</v>
       </c>
-      <c r="E18" s="57">
+      <c r="E18" s="56">
         <v>46275</v>
       </c>
-      <c r="F18" s="56" t="s">
+      <c r="F18" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="G18" s="55" t="s">
+      <c r="G18" s="54" t="s">
         <v>103</v>
       </c>
-      <c r="H18" s="55" t="s">
+      <c r="H18" s="54" t="s">
         <v>141</v>
       </c>
-      <c r="I18" s="55" t="s">
+      <c r="I18" s="54" t="s">
         <v>104</v>
       </c>
-      <c r="J18" s="21"/>
-      <c r="K18" s="21"/>
-      <c r="L18" s="21"/>
-      <c r="M18" s="23"/>
-      <c r="N18" s="23"/>
-      <c r="O18" s="23"/>
-      <c r="P18" s="56" t="s">
+      <c r="J18" s="20"/>
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+      <c r="M18" s="22"/>
+      <c r="N18" s="22"/>
+      <c r="O18" s="22"/>
+      <c r="P18" s="55" t="s">
         <v>148</v>
       </c>
-      <c r="Q18" s="23"/>
-      <c r="R18" s="23"/>
-      <c r="S18" s="23"/>
-      <c r="T18" s="23"/>
-      <c r="U18" s="23"/>
-      <c r="V18" s="23"/>
-      <c r="W18" s="23"/>
+      <c r="Q18" s="22"/>
+      <c r="R18" s="22"/>
+      <c r="S18" s="22"/>
+      <c r="T18" s="22"/>
+      <c r="U18" s="22"/>
+      <c r="V18" s="22"/>
+      <c r="W18" s="22"/>
     </row>
     <row r="19" spans="1:23" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="55" t="s">
+      <c r="A19" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="B19" s="55" t="s">
+      <c r="B19" s="54" t="s">
         <v>149</v>
       </c>
-      <c r="C19" s="56" t="s">
+      <c r="C19" s="55" t="s">
         <v>150</v>
       </c>
-      <c r="D19" s="58">
+      <c r="D19" s="57">
         <v>46276</v>
       </c>
-      <c r="E19" s="57">
+      <c r="E19" s="56">
         <v>46276</v>
       </c>
-      <c r="F19" s="56" t="s">
+      <c r="F19" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="G19" s="55" t="s">
+      <c r="G19" s="54" t="s">
         <v>103</v>
       </c>
-      <c r="H19" s="55" t="s">
+      <c r="H19" s="54" t="s">
         <v>141</v>
       </c>
-      <c r="I19" s="55" t="s">
+      <c r="I19" s="54" t="s">
         <v>112</v>
       </c>
-      <c r="J19" s="21"/>
-      <c r="K19" s="21"/>
-      <c r="L19" s="21"/>
-      <c r="M19" s="23"/>
-      <c r="N19" s="23"/>
-      <c r="O19" s="23"/>
-      <c r="P19" s="23"/>
-      <c r="Q19" s="56" t="s">
+      <c r="J19" s="20"/>
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+      <c r="M19" s="22"/>
+      <c r="N19" s="22"/>
+      <c r="O19" s="22"/>
+      <c r="P19" s="22"/>
+      <c r="Q19" s="55" t="s">
         <v>151</v>
       </c>
-      <c r="R19" s="23"/>
-      <c r="S19" s="23"/>
-      <c r="T19" s="23"/>
-      <c r="U19" s="23"/>
-      <c r="V19" s="23"/>
-      <c r="W19" s="23"/>
+      <c r="R19" s="22"/>
+      <c r="S19" s="22"/>
+      <c r="T19" s="22"/>
+      <c r="U19" s="22"/>
+      <c r="V19" s="22"/>
+      <c r="W19" s="22"/>
     </row>
     <row r="20" spans="1:23" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="55" t="s">
+      <c r="A20" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="B20" s="55" t="s">
+      <c r="B20" s="54" t="s">
         <v>152</v>
       </c>
-      <c r="C20" s="56" t="s">
+      <c r="C20" s="55" t="s">
         <v>153</v>
       </c>
-      <c r="D20" s="57">
+      <c r="D20" s="56">
         <v>46277</v>
       </c>
-      <c r="E20" s="57">
+      <c r="E20" s="56">
         <v>46278</v>
       </c>
-      <c r="F20" s="56" t="s">
+      <c r="F20" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="G20" s="16" t="s">
+      <c r="G20" s="15" t="s">
         <v>154</v>
       </c>
-      <c r="H20" s="55" t="s">
+      <c r="H20" s="54" t="s">
         <v>141</v>
       </c>
-      <c r="I20" s="55" t="s">
+      <c r="I20" s="54" t="s">
         <v>112</v>
       </c>
-      <c r="J20" s="21"/>
-      <c r="K20" s="21"/>
-      <c r="L20" s="21"/>
-      <c r="M20" s="23"/>
-      <c r="N20" s="23"/>
-      <c r="O20" s="23"/>
-      <c r="P20" s="23"/>
-      <c r="Q20" s="23"/>
-      <c r="R20" s="56" t="s">
+      <c r="J20" s="20"/>
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+      <c r="M20" s="22"/>
+      <c r="N20" s="22"/>
+      <c r="O20" s="22"/>
+      <c r="P20" s="22"/>
+      <c r="Q20" s="22"/>
+      <c r="R20" s="55" t="s">
         <v>155</v>
       </c>
-      <c r="S20" s="23"/>
-      <c r="T20" s="23"/>
-      <c r="U20" s="23"/>
-      <c r="V20" s="23"/>
-      <c r="W20" s="23"/>
+      <c r="S20" s="22"/>
+      <c r="T20" s="22"/>
+      <c r="U20" s="22"/>
+      <c r="V20" s="22"/>
+      <c r="W20" s="22"/>
     </row>
     <row r="21" spans="1:23" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="55" t="s">
+      <c r="A21" s="54" t="s">
         <v>64</v>
       </c>
-      <c r="B21" s="55" t="s">
+      <c r="B21" s="54" t="s">
         <v>156</v>
       </c>
-      <c r="C21" s="56" t="s">
+      <c r="C21" s="55" t="s">
         <v>157</v>
       </c>
-      <c r="D21" s="57">
+      <c r="D21" s="56">
         <v>46278</v>
       </c>
-      <c r="E21" s="57">
+      <c r="E21" s="56">
         <v>46278</v>
       </c>
-      <c r="F21" s="56" t="s">
+      <c r="F21" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="G21" s="55" t="s">
+      <c r="G21" s="54" t="s">
         <v>122</v>
       </c>
-      <c r="H21" s="55" t="s">
+      <c r="H21" s="54" t="s">
         <v>141</v>
       </c>
-      <c r="I21" s="55" t="s">
+      <c r="I21" s="54" t="s">
         <v>104</v>
       </c>
-      <c r="J21" s="21"/>
-      <c r="K21" s="21"/>
-      <c r="L21" s="21"/>
-      <c r="M21" s="23"/>
-      <c r="N21" s="23"/>
-      <c r="O21" s="23"/>
-      <c r="P21" s="23"/>
-      <c r="Q21" s="23"/>
-      <c r="R21" s="23"/>
-      <c r="S21" s="59" t="s">
+      <c r="J21" s="20"/>
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+      <c r="M21" s="22"/>
+      <c r="N21" s="22"/>
+      <c r="O21" s="22"/>
+      <c r="P21" s="22"/>
+      <c r="Q21" s="22"/>
+      <c r="R21" s="22"/>
+      <c r="S21" s="58" t="s">
         <v>158</v>
       </c>
-      <c r="T21" s="23"/>
-      <c r="U21" s="23"/>
-      <c r="V21" s="23"/>
-      <c r="W21" s="23"/>
+      <c r="T21" s="22"/>
+      <c r="U21" s="22"/>
+      <c r="V21" s="22"/>
+      <c r="W21" s="22"/>
     </row>
     <row r="22" spans="1:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="55" t="s">
+      <c r="A22" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="B22" s="55" t="s">
+      <c r="B22" s="54" t="s">
         <v>214</v>
       </c>
-      <c r="C22" s="56" t="s">
+      <c r="C22" s="55" t="s">
         <v>213</v>
       </c>
-      <c r="D22" s="57">
+      <c r="D22" s="56">
         <v>46279</v>
       </c>
-      <c r="E22" s="57">
+      <c r="E22" s="56">
         <v>46279</v>
       </c>
-      <c r="F22" s="56" t="s">
+      <c r="F22" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="G22" s="55" t="s">
+      <c r="G22" s="54" t="s">
         <v>103</v>
       </c>
-      <c r="H22" s="55" t="s">
+      <c r="H22" s="54" t="s">
         <v>141</v>
       </c>
-      <c r="I22" s="55" t="s">
+      <c r="I22" s="54" t="s">
         <v>108</v>
       </c>
-      <c r="J22" s="21"/>
-      <c r="K22" s="21"/>
-      <c r="L22" s="21"/>
-      <c r="M22" s="23"/>
-      <c r="N22" s="23"/>
-      <c r="O22" s="23"/>
-      <c r="P22" s="23"/>
-      <c r="Q22" s="23"/>
-      <c r="R22" s="23"/>
-      <c r="S22" s="59"/>
-      <c r="T22" s="23"/>
-      <c r="U22" s="23"/>
-      <c r="V22" s="23"/>
-      <c r="W22" s="23"/>
+      <c r="J22" s="20"/>
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+      <c r="M22" s="22"/>
+      <c r="N22" s="22"/>
+      <c r="O22" s="22"/>
+      <c r="P22" s="22"/>
+      <c r="Q22" s="22"/>
+      <c r="R22" s="22"/>
+      <c r="S22" s="58"/>
+      <c r="T22" s="22"/>
+      <c r="U22" s="22"/>
+      <c r="V22" s="22"/>
+      <c r="W22" s="22"/>
     </row>
     <row r="23" spans="1:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="55" t="s">
+      <c r="A23" s="54" t="s">
         <v>201</v>
       </c>
-      <c r="B23" s="55" t="s">
+      <c r="B23" s="54" t="s">
         <v>215</v>
       </c>
-      <c r="C23" s="56" t="s">
+      <c r="C23" s="55" t="s">
         <v>216</v>
       </c>
-      <c r="D23" s="57">
+      <c r="D23" s="56">
         <v>46280</v>
       </c>
-      <c r="E23" s="57">
+      <c r="E23" s="56">
         <v>46280</v>
       </c>
-      <c r="F23" s="20" t="s">
+      <c r="F23" s="19" t="s">
         <v>217</v>
       </c>
-      <c r="G23" s="55" t="s">
+      <c r="G23" s="54" t="s">
         <v>103</v>
       </c>
-      <c r="H23" s="20" t="s">
+      <c r="H23" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="I23" s="21" t="s">
+      <c r="I23" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="J23" s="21"/>
-      <c r="K23" s="21"/>
-      <c r="L23" s="21"/>
-      <c r="M23" s="23"/>
-      <c r="N23" s="23"/>
-      <c r="O23" s="23"/>
-      <c r="P23" s="23"/>
-      <c r="Q23" s="23"/>
-      <c r="R23" s="23"/>
-      <c r="S23" s="23"/>
-      <c r="T23" s="23"/>
-      <c r="U23" s="23"/>
-      <c r="V23" s="23"/>
-      <c r="W23" s="23"/>
+      <c r="J23" s="20"/>
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+      <c r="M23" s="22"/>
+      <c r="N23" s="22"/>
+      <c r="O23" s="22"/>
+      <c r="P23" s="22"/>
+      <c r="Q23" s="22"/>
+      <c r="R23" s="22"/>
+      <c r="S23" s="22"/>
+      <c r="T23" s="22"/>
+      <c r="U23" s="22"/>
+      <c r="V23" s="22"/>
+      <c r="W23" s="22"/>
     </row>
     <row r="24" spans="1:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="55" t="s">
+      <c r="A24" s="54" t="s">
         <v>202</v>
       </c>
-      <c r="B24" s="55" t="s">
+      <c r="B24" s="54" t="s">
         <v>218</v>
       </c>
-      <c r="C24" s="42" t="s">
+      <c r="C24" s="41" t="s">
         <v>219</v>
       </c>
-      <c r="D24" s="57">
+      <c r="D24" s="56">
         <v>46281</v>
       </c>
-      <c r="E24" s="57">
+      <c r="E24" s="56">
         <v>46281</v>
       </c>
-      <c r="F24" s="20" t="s">
+      <c r="F24" s="19" t="s">
         <v>217</v>
       </c>
-      <c r="G24" s="55" t="s">
+      <c r="G24" s="54" t="s">
         <v>103</v>
       </c>
-      <c r="H24" s="20" t="s">
+      <c r="H24" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="I24" s="21" t="s">
+      <c r="I24" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="J24" s="21"/>
-      <c r="K24" s="21"/>
-      <c r="L24" s="21"/>
-      <c r="M24" s="23"/>
-      <c r="N24" s="23"/>
-      <c r="O24" s="23"/>
-      <c r="P24" s="23"/>
-      <c r="Q24" s="23"/>
-      <c r="R24" s="23"/>
-      <c r="S24" s="23"/>
-      <c r="T24" s="23"/>
-      <c r="U24" s="23"/>
-      <c r="V24" s="23"/>
-      <c r="W24" s="23"/>
+      <c r="J24" s="20"/>
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+      <c r="M24" s="22"/>
+      <c r="N24" s="22"/>
+      <c r="O24" s="22"/>
+      <c r="P24" s="22"/>
+      <c r="Q24" s="22"/>
+      <c r="R24" s="22"/>
+      <c r="S24" s="22"/>
+      <c r="T24" s="22"/>
+      <c r="U24" s="22"/>
+      <c r="V24" s="22"/>
+      <c r="W24" s="22"/>
     </row>
     <row r="25" spans="1:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="55" t="s">
+      <c r="A25" s="54" t="s">
         <v>204</v>
       </c>
-      <c r="B25" s="55" t="s">
+      <c r="B25" s="54" t="s">
         <v>220</v>
       </c>
-      <c r="C25" s="55" t="s">
+      <c r="C25" s="54" t="s">
         <v>221</v>
       </c>
-      <c r="D25" s="57">
+      <c r="D25" s="56">
         <v>46282</v>
       </c>
-      <c r="E25" s="57">
+      <c r="E25" s="56">
         <v>46282</v>
       </c>
-      <c r="F25" s="20" t="s">
+      <c r="F25" s="19" t="s">
         <v>217</v>
       </c>
-      <c r="G25" s="55" t="s">
+      <c r="G25" s="54" t="s">
         <v>103</v>
       </c>
-      <c r="H25" s="20" t="s">
+      <c r="H25" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="I25" s="21" t="s">
+      <c r="I25" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="J25" s="21"/>
-      <c r="K25" s="21"/>
-      <c r="L25" s="21"/>
-      <c r="M25" s="23"/>
-      <c r="N25" s="23"/>
-      <c r="O25" s="23"/>
-      <c r="P25" s="23"/>
-      <c r="Q25" s="23"/>
-      <c r="R25" s="23"/>
-      <c r="S25" s="23"/>
-      <c r="T25" s="23"/>
-      <c r="U25" s="23"/>
-      <c r="V25" s="23"/>
-      <c r="W25" s="23"/>
+      <c r="J25" s="20"/>
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+      <c r="M25" s="22"/>
+      <c r="N25" s="22"/>
+      <c r="O25" s="22"/>
+      <c r="P25" s="22"/>
+      <c r="Q25" s="22"/>
+      <c r="R25" s="22"/>
+      <c r="S25" s="22"/>
+      <c r="T25" s="22"/>
+      <c r="U25" s="22"/>
+      <c r="V25" s="22"/>
+      <c r="W25" s="22"/>
     </row>
     <row r="26" spans="1:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="55" t="s">
+      <c r="A26" s="54" t="s">
         <v>209</v>
       </c>
-      <c r="B26" s="55" t="s">
+      <c r="B26" s="54" t="s">
         <v>222</v>
       </c>
-      <c r="C26" s="56" t="s">
+      <c r="C26" s="55" t="s">
         <v>223</v>
       </c>
-      <c r="D26" s="57">
+      <c r="D26" s="56">
         <v>46283</v>
       </c>
-      <c r="E26" s="57">
+      <c r="E26" s="56">
         <v>46283</v>
       </c>
-      <c r="F26" s="20" t="s">
+      <c r="F26" s="19" t="s">
         <v>217</v>
       </c>
-      <c r="G26" s="55" t="s">
+      <c r="G26" s="54" t="s">
         <v>103</v>
       </c>
-      <c r="H26" s="20" t="s">
+      <c r="H26" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="I26" s="21" t="s">
+      <c r="I26" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="J26" s="23"/>
-      <c r="K26" s="23"/>
-      <c r="L26" s="23"/>
-      <c r="M26" s="23"/>
-      <c r="N26" s="23"/>
-      <c r="O26" s="23"/>
-      <c r="P26" s="23"/>
-      <c r="Q26" s="23"/>
-      <c r="R26" s="23"/>
-      <c r="S26" s="23"/>
-      <c r="T26" s="23"/>
-      <c r="U26" s="23"/>
-      <c r="V26" s="23"/>
-      <c r="W26" s="23"/>
+      <c r="J26" s="22"/>
+      <c r="K26" s="22"/>
+      <c r="L26" s="22"/>
+      <c r="M26" s="22"/>
+      <c r="N26" s="22"/>
+      <c r="O26" s="22"/>
+      <c r="P26" s="22"/>
+      <c r="Q26" s="22"/>
+      <c r="R26" s="22"/>
+      <c r="S26" s="22"/>
+      <c r="T26" s="22"/>
+      <c r="U26" s="22"/>
+      <c r="V26" s="22"/>
+      <c r="W26" s="22"/>
     </row>
     <row r="27" spans="1:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="55" t="s">
+      <c r="A27" s="54" t="s">
         <v>211</v>
       </c>
-      <c r="B27" s="55" t="s">
+      <c r="B27" s="54" t="s">
         <v>224</v>
       </c>
-      <c r="C27" s="56" t="s">
+      <c r="C27" s="55" t="s">
         <v>225</v>
       </c>
-      <c r="D27" s="57">
+      <c r="D27" s="56">
         <v>46284</v>
       </c>
-      <c r="E27" s="57">
+      <c r="E27" s="56">
         <v>46284</v>
       </c>
-      <c r="F27" s="20" t="s">
+      <c r="F27" s="19" t="s">
         <v>217</v>
       </c>
-      <c r="G27" s="59" t="s">
+      <c r="G27" s="58" t="s">
         <v>122</v>
       </c>
-      <c r="H27" s="20" t="s">
+      <c r="H27" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="I27" s="55" t="s">
+      <c r="I27" s="54" t="s">
         <v>104</v>
       </c>
-      <c r="J27" s="23"/>
-      <c r="K27" s="23"/>
-      <c r="L27" s="23"/>
-      <c r="M27" s="23"/>
-      <c r="N27" s="23"/>
-      <c r="O27" s="23"/>
-      <c r="P27" s="23"/>
-      <c r="Q27" s="23"/>
-      <c r="R27" s="23"/>
-      <c r="S27" s="23"/>
-      <c r="T27" s="23"/>
-      <c r="U27" s="23"/>
-      <c r="V27" s="23"/>
-      <c r="W27" s="23"/>
+      <c r="J27" s="22"/>
+      <c r="K27" s="22"/>
+      <c r="L27" s="22"/>
+      <c r="M27" s="22"/>
+      <c r="N27" s="22"/>
+      <c r="O27" s="22"/>
+      <c r="P27" s="22"/>
+      <c r="Q27" s="22"/>
+      <c r="R27" s="22"/>
+      <c r="S27" s="22"/>
+      <c r="T27" s="22"/>
+      <c r="U27" s="22"/>
+      <c r="V27" s="22"/>
+      <c r="W27" s="22"/>
     </row>
     <row r="28" spans="1:23" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="55" t="s">
+      <c r="A28" s="54" t="s">
         <v>226</v>
       </c>
-      <c r="B28" s="55" t="s">
+      <c r="B28" s="54" t="s">
         <v>227</v>
       </c>
-      <c r="C28" s="56" t="s">
+      <c r="C28" s="55" t="s">
         <v>228</v>
       </c>
-      <c r="D28" s="57">
+      <c r="D28" s="56">
         <v>46285</v>
       </c>
-      <c r="E28" s="57">
+      <c r="E28" s="56">
         <v>46285</v>
       </c>
-      <c r="F28" s="20" t="s">
+      <c r="F28" s="19" t="s">
         <v>217</v>
       </c>
-      <c r="G28" s="59" t="s">
+      <c r="G28" s="58" t="s">
         <v>154</v>
       </c>
-      <c r="H28" s="20" t="s">
+      <c r="H28" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="I28" s="55" t="s">
+      <c r="I28" s="54" t="s">
         <v>104</v>
       </c>
-      <c r="J28" s="23"/>
-      <c r="K28" s="23"/>
-      <c r="L28" s="23"/>
-      <c r="M28" s="23"/>
-      <c r="N28" s="23"/>
-      <c r="O28" s="23"/>
-      <c r="P28" s="23"/>
-      <c r="Q28" s="23"/>
-      <c r="R28" s="23"/>
-      <c r="S28" s="23"/>
-      <c r="T28" s="23"/>
-      <c r="U28" s="23"/>
-      <c r="V28" s="23"/>
-      <c r="W28" s="23"/>
+      <c r="J28" s="22"/>
+      <c r="K28" s="22"/>
+      <c r="L28" s="22"/>
+      <c r="M28" s="22"/>
+      <c r="N28" s="22"/>
+      <c r="O28" s="22"/>
+      <c r="P28" s="22"/>
+      <c r="Q28" s="22"/>
+      <c r="R28" s="22"/>
+      <c r="S28" s="22"/>
+      <c r="T28" s="22"/>
+      <c r="U28" s="22"/>
+      <c r="V28" s="22"/>
+      <c r="W28" s="22"/>
     </row>
     <row r="29" spans="1:23" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="50"/>
-      <c r="B29" s="22"/>
-      <c r="C29" s="24" t="s">
+      <c r="A29" s="49" t="s">
+        <v>249</v>
+      </c>
+      <c r="B29" s="54" t="s">
+        <v>267</v>
+      </c>
+      <c r="C29" s="55" t="s">
+        <v>268</v>
+      </c>
+      <c r="D29" s="56">
+        <v>46286</v>
+      </c>
+      <c r="E29" s="56">
+        <v>46286</v>
+      </c>
+      <c r="F29" s="55" t="s">
+        <v>10</v>
+      </c>
+      <c r="G29" s="54" t="s">
+        <v>97</v>
+      </c>
+      <c r="H29" s="54" t="s">
+        <v>98</v>
+      </c>
+      <c r="I29" s="54" t="s">
+        <v>269</v>
+      </c>
+      <c r="J29" s="22"/>
+      <c r="K29" s="22"/>
+      <c r="L29" s="22"/>
+      <c r="M29" s="22"/>
+      <c r="N29" s="22"/>
+      <c r="O29" s="22"/>
+      <c r="P29" s="22"/>
+      <c r="Q29" s="22"/>
+      <c r="R29" s="22"/>
+      <c r="S29" s="22"/>
+      <c r="T29" s="22"/>
+      <c r="U29" s="22"/>
+      <c r="V29" s="22"/>
+      <c r="W29" s="22"/>
+    </row>
+    <row r="30" spans="1:23" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="54" t="s">
+        <v>249</v>
+      </c>
+      <c r="B30" s="54" t="s">
+        <v>270</v>
+      </c>
+      <c r="C30" s="54" t="s">
+        <v>271</v>
+      </c>
+      <c r="D30" s="56">
+        <v>46287</v>
+      </c>
+      <c r="E30" s="56">
+        <v>46288</v>
+      </c>
+      <c r="F30" s="55" t="s">
+        <v>10</v>
+      </c>
+      <c r="G30" s="54" t="s">
+        <v>272</v>
+      </c>
+      <c r="H30" s="54" t="s">
+        <v>263</v>
+      </c>
+      <c r="I30" s="54" t="s">
+        <v>99</v>
+      </c>
+      <c r="J30" s="22"/>
+      <c r="K30" s="22"/>
+      <c r="L30" s="22"/>
+      <c r="M30" s="22"/>
+      <c r="N30" s="22"/>
+      <c r="O30" s="22"/>
+      <c r="P30" s="22"/>
+      <c r="Q30" s="22"/>
+      <c r="R30" s="22"/>
+      <c r="S30" s="22"/>
+      <c r="T30" s="22"/>
+      <c r="U30" s="22"/>
+      <c r="V30" s="22"/>
+      <c r="W30" s="22"/>
+    </row>
+    <row r="31" spans="1:23" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="54" t="s">
+        <v>249</v>
+      </c>
+      <c r="B31" s="21" t="s">
+        <v>273</v>
+      </c>
+      <c r="C31" s="54" t="s">
+        <v>274</v>
+      </c>
+      <c r="D31" s="56">
+        <v>46289</v>
+      </c>
+      <c r="E31" s="56">
+        <v>46290</v>
+      </c>
+      <c r="F31" s="55" t="s">
+        <v>10</v>
+      </c>
+      <c r="G31" s="54" t="s">
+        <v>103</v>
+      </c>
+      <c r="H31" s="54" t="s">
+        <v>263</v>
+      </c>
+      <c r="I31" s="54" t="s">
+        <v>104</v>
+      </c>
+      <c r="J31" s="22"/>
+      <c r="K31" s="22"/>
+      <c r="L31" s="22"/>
+      <c r="M31" s="22"/>
+      <c r="N31" s="22"/>
+      <c r="O31" s="22"/>
+      <c r="P31" s="22"/>
+      <c r="Q31" s="22"/>
+      <c r="R31" s="22"/>
+      <c r="S31" s="22"/>
+      <c r="T31" s="22"/>
+      <c r="U31" s="22"/>
+      <c r="V31" s="22"/>
+      <c r="W31" s="22"/>
+    </row>
+    <row r="32" spans="1:23" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="54" t="s">
+        <v>252</v>
+      </c>
+      <c r="B32" s="21" t="s">
+        <v>276</v>
+      </c>
+      <c r="C32" s="54" t="s">
+        <v>275</v>
+      </c>
+      <c r="D32" s="56">
+        <v>46291</v>
+      </c>
+      <c r="E32" s="56">
+        <v>46292</v>
+      </c>
+      <c r="F32" s="55" t="s">
+        <v>10</v>
+      </c>
+      <c r="G32" s="54" t="s">
+        <v>103</v>
+      </c>
+      <c r="H32" s="54" t="s">
+        <v>98</v>
+      </c>
+      <c r="I32" s="54" t="s">
+        <v>99</v>
+      </c>
+      <c r="J32" s="22"/>
+      <c r="K32" s="22"/>
+      <c r="L32" s="22"/>
+      <c r="M32" s="22"/>
+      <c r="N32" s="22"/>
+      <c r="O32" s="22"/>
+      <c r="P32" s="22"/>
+      <c r="Q32" s="22"/>
+      <c r="R32" s="22"/>
+      <c r="S32" s="22"/>
+      <c r="T32" s="22"/>
+      <c r="U32" s="22"/>
+      <c r="V32" s="22"/>
+      <c r="W32" s="22"/>
+    </row>
+    <row r="33" spans="1:23" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="54" t="s">
+        <v>255</v>
+      </c>
+      <c r="B33" s="21" t="s">
+        <v>277</v>
+      </c>
+      <c r="C33" s="54" t="s">
+        <v>278</v>
+      </c>
+      <c r="D33" s="56">
+        <v>46293</v>
+      </c>
+      <c r="E33" s="56">
+        <v>46294</v>
+      </c>
+      <c r="F33" s="55" t="s">
+        <v>10</v>
+      </c>
+      <c r="G33" s="54" t="s">
+        <v>103</v>
+      </c>
+      <c r="H33" s="54" t="s">
+        <v>98</v>
+      </c>
+      <c r="I33" s="54" t="s">
+        <v>99</v>
+      </c>
+      <c r="J33" s="22"/>
+      <c r="K33" s="22"/>
+      <c r="L33" s="22"/>
+      <c r="M33" s="22"/>
+      <c r="N33" s="22"/>
+      <c r="O33" s="22"/>
+      <c r="P33" s="22"/>
+      <c r="Q33" s="22"/>
+      <c r="R33" s="22"/>
+      <c r="S33" s="22"/>
+      <c r="T33" s="22"/>
+      <c r="U33" s="22"/>
+      <c r="V33" s="22"/>
+      <c r="W33" s="22"/>
+    </row>
+    <row r="34" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="54" t="s">
+        <v>257</v>
+      </c>
+      <c r="B34" s="21" t="s">
+        <v>280</v>
+      </c>
+      <c r="C34" s="55" t="s">
+        <v>279</v>
+      </c>
+      <c r="D34" s="56">
+        <v>46295</v>
+      </c>
+      <c r="E34" s="56">
+        <v>46296</v>
+      </c>
+      <c r="F34" s="55" t="s">
+        <v>10</v>
+      </c>
+      <c r="G34" s="54" t="s">
+        <v>103</v>
+      </c>
+      <c r="H34" s="54" t="s">
+        <v>263</v>
+      </c>
+      <c r="I34" s="54" t="s">
+        <v>99</v>
+      </c>
+      <c r="J34" s="22"/>
+      <c r="K34" s="22"/>
+      <c r="L34" s="22"/>
+      <c r="M34" s="22"/>
+      <c r="N34" s="22"/>
+      <c r="O34" s="22"/>
+      <c r="P34" s="22"/>
+      <c r="Q34" s="22"/>
+      <c r="R34" s="22"/>
+      <c r="S34" s="22"/>
+      <c r="T34" s="22"/>
+      <c r="U34" s="22"/>
+      <c r="V34" s="22"/>
+      <c r="W34" s="22"/>
+    </row>
+    <row r="35" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="54" t="s">
+        <v>261</v>
+      </c>
+      <c r="B35" s="21" t="s">
+        <v>281</v>
+      </c>
+      <c r="C35" s="54" t="s">
+        <v>282</v>
+      </c>
+      <c r="D35" s="56">
+        <v>46297</v>
+      </c>
+      <c r="E35" s="56">
+        <v>46298</v>
+      </c>
+      <c r="F35" s="55" t="s">
+        <v>10</v>
+      </c>
+      <c r="G35" s="54" t="s">
+        <v>103</v>
+      </c>
+      <c r="H35" s="54" t="s">
+        <v>263</v>
+      </c>
+      <c r="I35" s="54" t="s">
+        <v>99</v>
+      </c>
+      <c r="J35" s="22"/>
+      <c r="K35" s="22"/>
+      <c r="L35" s="22"/>
+      <c r="M35" s="22"/>
+      <c r="N35" s="22"/>
+      <c r="O35" s="22"/>
+      <c r="P35" s="22"/>
+      <c r="Q35" s="22"/>
+      <c r="R35" s="22"/>
+      <c r="S35" s="22"/>
+      <c r="T35" s="22"/>
+      <c r="U35" s="22"/>
+      <c r="V35" s="22"/>
+      <c r="W35" s="22"/>
+    </row>
+    <row r="36" spans="1:23" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="54" t="s">
+        <v>264</v>
+      </c>
+      <c r="B36" s="21" t="s">
+        <v>284</v>
+      </c>
+      <c r="C36" s="55" t="s">
+        <v>286</v>
+      </c>
+      <c r="D36" s="56">
+        <v>46299</v>
+      </c>
+      <c r="E36" s="56">
+        <v>46300</v>
+      </c>
+      <c r="F36" s="55" t="s">
+        <v>10</v>
+      </c>
+      <c r="G36" s="54" t="s">
+        <v>122</v>
+      </c>
+      <c r="H36" s="54" t="s">
+        <v>98</v>
+      </c>
+      <c r="I36" s="54" t="s">
+        <v>112</v>
+      </c>
+      <c r="J36" s="22"/>
+      <c r="K36" s="22"/>
+      <c r="L36" s="22"/>
+      <c r="M36" s="22"/>
+      <c r="N36" s="22"/>
+      <c r="O36" s="22"/>
+      <c r="P36" s="22"/>
+      <c r="Q36" s="22"/>
+      <c r="R36" s="22"/>
+      <c r="S36" s="22"/>
+      <c r="T36" s="22"/>
+      <c r="U36" s="22"/>
+      <c r="V36" s="22"/>
+      <c r="W36" s="22"/>
+    </row>
+    <row r="37" spans="1:23" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="54" t="s">
+        <v>283</v>
+      </c>
+      <c r="B37" s="21" t="s">
+        <v>285</v>
+      </c>
+      <c r="C37" s="55" t="s">
+        <v>287</v>
+      </c>
+      <c r="D37" s="56">
+        <v>46301</v>
+      </c>
+      <c r="E37" s="56">
+        <v>46301</v>
+      </c>
+      <c r="F37" s="55" t="s">
+        <v>10</v>
+      </c>
+      <c r="G37" s="54" t="s">
+        <v>154</v>
+      </c>
+      <c r="H37" s="54" t="s">
+        <v>98</v>
+      </c>
+      <c r="I37" s="54" t="s">
+        <v>112</v>
+      </c>
+      <c r="J37" s="22"/>
+      <c r="K37" s="22"/>
+      <c r="L37" s="22"/>
+      <c r="M37" s="22"/>
+      <c r="N37" s="22"/>
+      <c r="O37" s="22"/>
+      <c r="P37" s="22"/>
+      <c r="Q37" s="22"/>
+      <c r="R37" s="22"/>
+      <c r="S37" s="22"/>
+      <c r="T37" s="22"/>
+      <c r="U37" s="22"/>
+      <c r="V37" s="22"/>
+      <c r="W37" s="22"/>
+    </row>
+    <row r="38" spans="1:23" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="49"/>
+      <c r="B38" s="21"/>
+      <c r="C38" s="23"/>
+      <c r="D38" s="41"/>
+      <c r="E38" s="41"/>
+      <c r="F38" s="18"/>
+      <c r="G38" s="17"/>
+      <c r="H38" s="19"/>
+      <c r="I38" s="20"/>
+      <c r="J38" s="22"/>
+      <c r="K38" s="22"/>
+      <c r="L38" s="22"/>
+      <c r="M38" s="22"/>
+      <c r="N38" s="22"/>
+      <c r="O38" s="22"/>
+      <c r="P38" s="22"/>
+      <c r="Q38" s="22"/>
+      <c r="R38" s="22"/>
+      <c r="S38" s="22"/>
+      <c r="T38" s="22"/>
+      <c r="U38" s="22"/>
+      <c r="V38" s="22"/>
+      <c r="W38" s="22"/>
+    </row>
+    <row r="39" spans="1:23" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="49"/>
+      <c r="B39" s="21"/>
+      <c r="C39" s="23"/>
+      <c r="D39" s="41"/>
+      <c r="E39" s="41"/>
+      <c r="F39" s="18"/>
+      <c r="G39" s="17"/>
+      <c r="H39" s="19"/>
+      <c r="I39" s="20"/>
+      <c r="J39" s="22"/>
+      <c r="K39" s="22"/>
+      <c r="L39" s="22"/>
+      <c r="M39" s="22"/>
+      <c r="N39" s="22"/>
+      <c r="O39" s="22"/>
+      <c r="P39" s="22"/>
+      <c r="Q39" s="22"/>
+      <c r="R39" s="22"/>
+      <c r="S39" s="22"/>
+      <c r="T39" s="22"/>
+      <c r="U39" s="22"/>
+      <c r="V39" s="22"/>
+      <c r="W39" s="22"/>
+    </row>
+    <row r="40" spans="1:23" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="49"/>
+      <c r="B40" s="21"/>
+      <c r="C40" s="23"/>
+      <c r="D40" s="41"/>
+      <c r="E40" s="41"/>
+      <c r="F40" s="18"/>
+      <c r="G40" s="17"/>
+      <c r="H40" s="19"/>
+      <c r="I40" s="20"/>
+      <c r="J40" s="22"/>
+      <c r="K40" s="22"/>
+      <c r="L40" s="22"/>
+      <c r="M40" s="22"/>
+      <c r="N40" s="22"/>
+      <c r="O40" s="22"/>
+      <c r="P40" s="22"/>
+      <c r="Q40" s="22"/>
+      <c r="R40" s="22"/>
+      <c r="S40" s="22"/>
+      <c r="T40" s="22"/>
+      <c r="U40" s="22"/>
+      <c r="V40" s="22"/>
+      <c r="W40" s="22"/>
+    </row>
+    <row r="41" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="49"/>
+      <c r="B41" s="21"/>
+      <c r="C41" s="23" t="s">
         <v>159</v>
       </c>
-      <c r="D29" s="42"/>
-      <c r="E29" s="42"/>
-      <c r="F29" s="19"/>
-      <c r="G29" s="59"/>
-      <c r="H29" s="20"/>
-      <c r="I29" s="21"/>
-      <c r="J29" s="23"/>
-      <c r="K29" s="23"/>
-      <c r="L29" s="23"/>
-      <c r="M29" s="23"/>
-      <c r="N29" s="23"/>
-      <c r="O29" s="23"/>
-      <c r="P29" s="23"/>
-      <c r="Q29" s="23"/>
-      <c r="R29" s="23"/>
-      <c r="S29" s="23"/>
-      <c r="T29" s="23"/>
-      <c r="U29" s="23"/>
-      <c r="V29" s="23"/>
-      <c r="W29" s="23"/>
-    </row>
-    <row r="30" spans="1:23" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="50"/>
-      <c r="B30" s="22"/>
-      <c r="C30" s="24"/>
-      <c r="D30" s="42"/>
-      <c r="E30" s="42"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="18"/>
-      <c r="H30" s="20"/>
-      <c r="I30" s="21"/>
-      <c r="J30" s="23"/>
-      <c r="K30" s="23"/>
-      <c r="L30" s="23"/>
-      <c r="M30" s="23"/>
-      <c r="N30" s="23"/>
-      <c r="O30" s="23"/>
-      <c r="P30" s="23"/>
-      <c r="Q30" s="23"/>
-      <c r="R30" s="23"/>
-      <c r="S30" s="23"/>
-      <c r="T30" s="23"/>
-      <c r="U30" s="23"/>
-      <c r="V30" s="23"/>
-      <c r="W30" s="23"/>
-    </row>
-    <row r="31" spans="1:23" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="50"/>
-      <c r="B31" s="22"/>
-      <c r="C31" s="24"/>
-      <c r="D31" s="42"/>
-      <c r="E31" s="42"/>
-      <c r="F31" s="19"/>
-      <c r="G31" s="18"/>
-      <c r="H31" s="20"/>
-      <c r="I31" s="21"/>
-      <c r="J31" s="23"/>
-      <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
-      <c r="N31" s="23"/>
-      <c r="O31" s="23"/>
-      <c r="P31" s="23"/>
-      <c r="Q31" s="23"/>
-      <c r="R31" s="23"/>
-      <c r="S31" s="23"/>
-      <c r="T31" s="23"/>
-      <c r="U31" s="23"/>
-      <c r="V31" s="23"/>
-      <c r="W31" s="23"/>
-    </row>
-    <row r="32" spans="1:23" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="50"/>
-      <c r="B32" s="22"/>
-      <c r="C32" s="24"/>
-      <c r="D32" s="42"/>
-      <c r="E32" s="42"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="18"/>
-      <c r="H32" s="20"/>
-      <c r="I32" s="21"/>
-      <c r="J32" s="23"/>
-      <c r="K32" s="23"/>
-      <c r="L32" s="23"/>
-      <c r="M32" s="23"/>
-      <c r="N32" s="23"/>
-      <c r="O32" s="23"/>
-      <c r="P32" s="23"/>
-      <c r="Q32" s="23"/>
-      <c r="R32" s="23"/>
-      <c r="S32" s="23"/>
-      <c r="T32" s="23"/>
-      <c r="U32" s="23"/>
-      <c r="V32" s="23"/>
-      <c r="W32" s="23"/>
-    </row>
-    <row r="33" spans="1:23" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="50"/>
-      <c r="B33" s="22"/>
-      <c r="C33" s="24"/>
-      <c r="D33" s="42"/>
-      <c r="E33" s="42"/>
-      <c r="F33" s="19"/>
-      <c r="G33" s="18"/>
-      <c r="H33" s="20"/>
-      <c r="I33" s="21"/>
-      <c r="J33" s="23"/>
-      <c r="K33" s="23"/>
-      <c r="L33" s="23"/>
-      <c r="M33" s="23"/>
-      <c r="N33" s="23"/>
-      <c r="O33" s="23"/>
-      <c r="P33" s="23"/>
-      <c r="Q33" s="23"/>
-      <c r="R33" s="23"/>
-      <c r="S33" s="23"/>
-      <c r="T33" s="23"/>
-      <c r="U33" s="23"/>
-      <c r="V33" s="23"/>
-      <c r="W33" s="23"/>
-    </row>
-    <row r="34" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="50"/>
-      <c r="B34" s="22"/>
-      <c r="C34" s="24" t="s">
+      <c r="D41" s="41"/>
+      <c r="E41" s="41"/>
+      <c r="F41" s="18"/>
+      <c r="G41" s="17"/>
+      <c r="H41" s="19"/>
+      <c r="I41" s="20"/>
+      <c r="J41" s="22"/>
+      <c r="K41" s="22"/>
+      <c r="L41" s="22"/>
+      <c r="M41" s="22"/>
+      <c r="N41" s="22"/>
+      <c r="O41" s="22"/>
+      <c r="P41" s="22"/>
+      <c r="Q41" s="22"/>
+      <c r="R41" s="22"/>
+      <c r="S41" s="22"/>
+      <c r="T41" s="22"/>
+      <c r="U41" s="22"/>
+      <c r="V41" s="22"/>
+      <c r="W41" s="22"/>
+    </row>
+    <row r="42" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="49"/>
+      <c r="B42" s="21"/>
+      <c r="C42" s="23" t="s">
         <v>159</v>
       </c>
-      <c r="D34" s="42"/>
-      <c r="E34" s="42"/>
-      <c r="F34" s="19"/>
-      <c r="G34" s="18"/>
-      <c r="H34" s="20"/>
-      <c r="I34" s="21"/>
-      <c r="J34" s="23"/>
-      <c r="K34" s="23"/>
-      <c r="L34" s="23"/>
-      <c r="M34" s="23"/>
-      <c r="N34" s="23"/>
-      <c r="O34" s="23"/>
-      <c r="P34" s="23"/>
-      <c r="Q34" s="23"/>
-      <c r="R34" s="23"/>
-      <c r="S34" s="23"/>
-      <c r="T34" s="23"/>
-      <c r="U34" s="23"/>
-      <c r="V34" s="23"/>
-      <c r="W34" s="23"/>
-    </row>
-    <row r="35" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="50"/>
-      <c r="B35" s="22"/>
-      <c r="C35" s="24" t="s">
+      <c r="D42" s="41"/>
+      <c r="E42" s="41"/>
+      <c r="F42" s="18"/>
+      <c r="G42" s="17"/>
+      <c r="H42" s="19"/>
+      <c r="I42" s="20"/>
+      <c r="J42" s="22"/>
+      <c r="K42" s="22"/>
+      <c r="L42" s="22"/>
+      <c r="M42" s="22"/>
+      <c r="N42" s="22"/>
+      <c r="O42" s="22"/>
+      <c r="P42" s="22"/>
+      <c r="Q42" s="22"/>
+      <c r="R42" s="22"/>
+      <c r="S42" s="22"/>
+      <c r="T42" s="22"/>
+      <c r="U42" s="22"/>
+      <c r="V42" s="22"/>
+      <c r="W42" s="22"/>
+    </row>
+    <row r="43" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="49"/>
+      <c r="B43" s="21"/>
+      <c r="C43" s="23" t="s">
         <v>159</v>
       </c>
-      <c r="D35" s="42"/>
-      <c r="E35" s="42"/>
-      <c r="F35" s="19"/>
-      <c r="G35" s="18"/>
-      <c r="H35" s="20"/>
-      <c r="I35" s="21"/>
-      <c r="J35" s="23"/>
-      <c r="K35" s="23"/>
-      <c r="L35" s="23"/>
-      <c r="M35" s="23"/>
-      <c r="N35" s="23"/>
-      <c r="O35" s="23"/>
-      <c r="P35" s="23"/>
-      <c r="Q35" s="23"/>
-      <c r="R35" s="23"/>
-      <c r="S35" s="23"/>
-      <c r="T35" s="23"/>
-      <c r="U35" s="23"/>
-      <c r="V35" s="23"/>
-      <c r="W35" s="23"/>
-    </row>
-    <row r="36" spans="1:23" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="50"/>
-      <c r="B36" s="22"/>
-      <c r="C36" s="24" t="s">
+      <c r="D43" s="41"/>
+      <c r="E43" s="41"/>
+      <c r="F43" s="18"/>
+      <c r="G43" s="17"/>
+      <c r="H43" s="19"/>
+      <c r="I43" s="20"/>
+      <c r="J43" s="22"/>
+      <c r="K43" s="22"/>
+      <c r="L43" s="22"/>
+      <c r="M43" s="22"/>
+      <c r="N43" s="22"/>
+      <c r="O43" s="22"/>
+      <c r="P43" s="22"/>
+      <c r="Q43" s="22"/>
+      <c r="R43" s="22"/>
+      <c r="S43" s="22"/>
+      <c r="T43" s="22"/>
+      <c r="U43" s="22"/>
+      <c r="V43" s="22"/>
+      <c r="W43" s="22"/>
+    </row>
+    <row r="44" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="49"/>
+      <c r="B44" s="21"/>
+      <c r="C44" s="23"/>
+      <c r="D44" s="41"/>
+      <c r="E44" s="41"/>
+      <c r="F44" s="18"/>
+      <c r="G44" s="17"/>
+      <c r="H44" s="19"/>
+      <c r="I44" s="20"/>
+      <c r="J44" s="22"/>
+      <c r="K44" s="22"/>
+      <c r="L44" s="22"/>
+      <c r="M44" s="22"/>
+      <c r="N44" s="22"/>
+      <c r="O44" s="22"/>
+      <c r="P44" s="22"/>
+      <c r="Q44" s="22"/>
+      <c r="R44" s="22"/>
+      <c r="S44" s="22"/>
+      <c r="T44" s="22"/>
+      <c r="U44" s="22"/>
+      <c r="V44" s="22"/>
+      <c r="W44" s="22"/>
+    </row>
+    <row r="45" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="49"/>
+      <c r="B45" s="21"/>
+      <c r="C45" s="23"/>
+      <c r="D45" s="41"/>
+      <c r="E45" s="41"/>
+      <c r="F45" s="18"/>
+      <c r="G45" s="17"/>
+      <c r="H45" s="19"/>
+      <c r="I45" s="20"/>
+      <c r="J45" s="22"/>
+      <c r="K45" s="22"/>
+      <c r="L45" s="22"/>
+      <c r="M45" s="22"/>
+      <c r="N45" s="22"/>
+      <c r="O45" s="22"/>
+      <c r="P45" s="22"/>
+      <c r="Q45" s="22"/>
+      <c r="R45" s="22"/>
+      <c r="S45" s="22"/>
+      <c r="T45" s="22"/>
+      <c r="U45" s="22"/>
+      <c r="V45" s="22"/>
+      <c r="W45" s="22"/>
+    </row>
+    <row r="46" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="49"/>
+      <c r="B46" s="21"/>
+      <c r="C46" s="23"/>
+      <c r="D46" s="41"/>
+      <c r="E46" s="41"/>
+      <c r="F46" s="18"/>
+      <c r="G46" s="17"/>
+      <c r="H46" s="19"/>
+      <c r="I46" s="20"/>
+      <c r="J46" s="22"/>
+      <c r="K46" s="22"/>
+      <c r="L46" s="22"/>
+      <c r="M46" s="22"/>
+      <c r="N46" s="22"/>
+      <c r="O46" s="22"/>
+      <c r="P46" s="22"/>
+      <c r="Q46" s="22"/>
+      <c r="R46" s="22"/>
+      <c r="S46" s="22"/>
+      <c r="T46" s="22"/>
+      <c r="U46" s="22"/>
+      <c r="V46" s="22"/>
+      <c r="W46" s="22"/>
+    </row>
+    <row r="47" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="49"/>
+      <c r="B47" s="21"/>
+      <c r="C47" s="23"/>
+      <c r="D47" s="41"/>
+      <c r="E47" s="41"/>
+      <c r="F47" s="18"/>
+      <c r="G47" s="17"/>
+      <c r="H47" s="19"/>
+      <c r="I47" s="20"/>
+      <c r="J47" s="22"/>
+      <c r="K47" s="22"/>
+      <c r="L47" s="22"/>
+      <c r="M47" s="22"/>
+      <c r="N47" s="22"/>
+      <c r="O47" s="22"/>
+      <c r="P47" s="22"/>
+      <c r="Q47" s="22"/>
+      <c r="R47" s="22"/>
+      <c r="S47" s="22"/>
+      <c r="T47" s="22"/>
+      <c r="U47" s="22"/>
+      <c r="V47" s="22"/>
+      <c r="W47" s="22"/>
+    </row>
+    <row r="48" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="49"/>
+      <c r="B48" s="21"/>
+      <c r="C48" s="23" t="s">
         <v>159</v>
       </c>
-      <c r="D36" s="42"/>
-      <c r="E36" s="42"/>
-      <c r="F36" s="19"/>
-      <c r="G36" s="18"/>
-      <c r="H36" s="20"/>
-      <c r="I36" s="21"/>
-      <c r="J36" s="23"/>
-      <c r="K36" s="23"/>
-      <c r="L36" s="23"/>
-      <c r="M36" s="23"/>
-      <c r="N36" s="23"/>
-      <c r="O36" s="23"/>
-      <c r="P36" s="23"/>
-      <c r="Q36" s="23"/>
-      <c r="R36" s="23"/>
-      <c r="S36" s="23"/>
-      <c r="T36" s="23"/>
-      <c r="U36" s="23"/>
-      <c r="V36" s="23"/>
-      <c r="W36" s="23"/>
-    </row>
-    <row r="37" spans="1:23" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="50"/>
-      <c r="B37" s="22"/>
-      <c r="C37" s="24"/>
-      <c r="D37" s="42"/>
-      <c r="E37" s="42"/>
-      <c r="F37" s="19"/>
-      <c r="G37" s="18"/>
-      <c r="H37" s="20"/>
-      <c r="I37" s="21"/>
-      <c r="J37" s="23"/>
-      <c r="K37" s="23"/>
-      <c r="L37" s="23"/>
-      <c r="M37" s="23"/>
-      <c r="N37" s="23"/>
-      <c r="O37" s="23"/>
-      <c r="P37" s="23"/>
-      <c r="Q37" s="23"/>
-      <c r="R37" s="23"/>
-      <c r="S37" s="23"/>
-      <c r="T37" s="23"/>
-      <c r="U37" s="23"/>
-      <c r="V37" s="23"/>
-      <c r="W37" s="23"/>
-    </row>
-    <row r="38" spans="1:23" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="50"/>
-      <c r="B38" s="22"/>
-      <c r="C38" s="24"/>
-      <c r="D38" s="42"/>
-      <c r="E38" s="42"/>
-      <c r="F38" s="19"/>
-      <c r="G38" s="18"/>
-      <c r="H38" s="20"/>
-      <c r="I38" s="21"/>
-      <c r="J38" s="23"/>
-      <c r="K38" s="23"/>
-      <c r="L38" s="23"/>
-      <c r="M38" s="23"/>
-      <c r="N38" s="23"/>
-      <c r="O38" s="23"/>
-      <c r="P38" s="23"/>
-      <c r="Q38" s="23"/>
-      <c r="R38" s="23"/>
-      <c r="S38" s="23"/>
-      <c r="T38" s="23"/>
-      <c r="U38" s="23"/>
-      <c r="V38" s="23"/>
-      <c r="W38" s="23"/>
-    </row>
-    <row r="39" spans="1:23" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="50"/>
-      <c r="B39" s="22"/>
-      <c r="C39" s="24"/>
-      <c r="D39" s="42"/>
-      <c r="E39" s="42"/>
-      <c r="F39" s="19"/>
-      <c r="G39" s="18"/>
-      <c r="H39" s="20"/>
-      <c r="I39" s="21"/>
-      <c r="J39" s="23"/>
-      <c r="K39" s="23"/>
-      <c r="L39" s="23"/>
-      <c r="M39" s="23"/>
-      <c r="N39" s="23"/>
-      <c r="O39" s="23"/>
-      <c r="P39" s="23"/>
-      <c r="Q39" s="23"/>
-      <c r="R39" s="23"/>
-      <c r="S39" s="23"/>
-      <c r="T39" s="23"/>
-      <c r="U39" s="23"/>
-      <c r="V39" s="23"/>
-      <c r="W39" s="23"/>
-    </row>
-    <row r="40" spans="1:23" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="50"/>
-      <c r="B40" s="22"/>
-      <c r="C40" s="24"/>
-      <c r="D40" s="42"/>
-      <c r="E40" s="42"/>
-      <c r="F40" s="19"/>
-      <c r="G40" s="18"/>
-      <c r="H40" s="20"/>
-      <c r="I40" s="21"/>
-      <c r="J40" s="23"/>
-      <c r="K40" s="23"/>
-      <c r="L40" s="23"/>
-      <c r="M40" s="23"/>
-      <c r="N40" s="23"/>
-      <c r="O40" s="23"/>
-      <c r="P40" s="23"/>
-      <c r="Q40" s="23"/>
-      <c r="R40" s="23"/>
-      <c r="S40" s="23"/>
-      <c r="T40" s="23"/>
-      <c r="U40" s="23"/>
-      <c r="V40" s="23"/>
-      <c r="W40" s="23"/>
-    </row>
-    <row r="41" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="50"/>
-      <c r="B41" s="22"/>
-      <c r="C41" s="24" t="s">
+      <c r="D48" s="41"/>
+      <c r="E48" s="41"/>
+      <c r="F48" s="18"/>
+      <c r="G48" s="17"/>
+      <c r="H48" s="19"/>
+      <c r="I48" s="20"/>
+      <c r="J48" s="22"/>
+      <c r="K48" s="22"/>
+      <c r="L48" s="22"/>
+      <c r="M48" s="22"/>
+      <c r="N48" s="22"/>
+      <c r="O48" s="22"/>
+      <c r="P48" s="22"/>
+      <c r="Q48" s="22"/>
+      <c r="R48" s="22"/>
+      <c r="S48" s="22"/>
+      <c r="T48" s="22"/>
+      <c r="U48" s="22"/>
+      <c r="V48" s="22"/>
+      <c r="W48" s="22"/>
+    </row>
+    <row r="49" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="49"/>
+      <c r="B49" s="21"/>
+      <c r="C49" s="23" t="s">
         <v>159</v>
       </c>
-      <c r="D41" s="42"/>
-      <c r="E41" s="42"/>
-      <c r="F41" s="19"/>
-      <c r="G41" s="18"/>
-      <c r="H41" s="20"/>
-      <c r="I41" s="21"/>
-      <c r="J41" s="23"/>
-      <c r="K41" s="23"/>
-      <c r="L41" s="23"/>
-      <c r="M41" s="23"/>
-      <c r="N41" s="23"/>
-      <c r="O41" s="23"/>
-      <c r="P41" s="23"/>
-      <c r="Q41" s="23"/>
-      <c r="R41" s="23"/>
-      <c r="S41" s="23"/>
-      <c r="T41" s="23"/>
-      <c r="U41" s="23"/>
-      <c r="V41" s="23"/>
-      <c r="W41" s="23"/>
-    </row>
-    <row r="42" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="50"/>
-      <c r="B42" s="22"/>
-      <c r="C42" s="24" t="s">
+      <c r="D49" s="41"/>
+      <c r="E49" s="41"/>
+      <c r="F49" s="18"/>
+      <c r="G49" s="17"/>
+      <c r="H49" s="19"/>
+      <c r="I49" s="20"/>
+      <c r="J49" s="22"/>
+      <c r="K49" s="22"/>
+      <c r="L49" s="22"/>
+      <c r="M49" s="22"/>
+      <c r="N49" s="22"/>
+      <c r="O49" s="22"/>
+      <c r="P49" s="22"/>
+      <c r="Q49" s="22"/>
+      <c r="R49" s="22"/>
+      <c r="S49" s="22"/>
+      <c r="T49" s="22"/>
+      <c r="U49" s="22"/>
+      <c r="V49" s="22"/>
+      <c r="W49" s="22"/>
+    </row>
+    <row r="50" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="49"/>
+      <c r="B50" s="21"/>
+      <c r="C50" s="23" t="s">
         <v>159</v>
       </c>
-      <c r="D42" s="42"/>
-      <c r="E42" s="42"/>
-      <c r="F42" s="19"/>
-      <c r="G42" s="18"/>
-      <c r="H42" s="20"/>
-      <c r="I42" s="21"/>
-      <c r="J42" s="23"/>
-      <c r="K42" s="23"/>
-      <c r="L42" s="23"/>
-      <c r="M42" s="23"/>
-      <c r="N42" s="23"/>
-      <c r="O42" s="23"/>
-      <c r="P42" s="23"/>
-      <c r="Q42" s="23"/>
-      <c r="R42" s="23"/>
-      <c r="S42" s="23"/>
-      <c r="T42" s="23"/>
-      <c r="U42" s="23"/>
-      <c r="V42" s="23"/>
-      <c r="W42" s="23"/>
-    </row>
-    <row r="43" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="50"/>
-      <c r="B43" s="22"/>
-      <c r="C43" s="24" t="s">
+      <c r="D50" s="41"/>
+      <c r="E50" s="41"/>
+      <c r="F50" s="18"/>
+      <c r="G50" s="17"/>
+      <c r="H50" s="19"/>
+      <c r="I50" s="20"/>
+      <c r="J50" s="22"/>
+      <c r="K50" s="22"/>
+      <c r="L50" s="22"/>
+      <c r="M50" s="22"/>
+      <c r="N50" s="22"/>
+      <c r="O50" s="22"/>
+      <c r="P50" s="22"/>
+      <c r="Q50" s="22"/>
+      <c r="R50" s="22"/>
+      <c r="S50" s="22"/>
+      <c r="T50" s="22"/>
+      <c r="U50" s="22"/>
+      <c r="V50" s="22"/>
+      <c r="W50" s="22"/>
+    </row>
+    <row r="51" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="49"/>
+      <c r="B51" s="21"/>
+      <c r="C51" s="23"/>
+      <c r="D51" s="41"/>
+      <c r="E51" s="41"/>
+      <c r="F51" s="18"/>
+      <c r="G51" s="17"/>
+      <c r="H51" s="19"/>
+      <c r="I51" s="20"/>
+      <c r="J51" s="22"/>
+      <c r="K51" s="22"/>
+      <c r="L51" s="22"/>
+      <c r="M51" s="22"/>
+      <c r="N51" s="22"/>
+      <c r="O51" s="22"/>
+      <c r="P51" s="22"/>
+      <c r="Q51" s="22"/>
+      <c r="R51" s="22"/>
+      <c r="S51" s="22"/>
+      <c r="T51" s="22"/>
+      <c r="U51" s="22"/>
+      <c r="V51" s="22"/>
+      <c r="W51" s="22"/>
+    </row>
+    <row r="52" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="49"/>
+      <c r="B52" s="21"/>
+      <c r="C52" s="23"/>
+      <c r="D52" s="41"/>
+      <c r="E52" s="41"/>
+      <c r="F52" s="18"/>
+      <c r="G52" s="17"/>
+      <c r="H52" s="19"/>
+      <c r="I52" s="20"/>
+      <c r="J52" s="22"/>
+      <c r="K52" s="22"/>
+      <c r="L52" s="22"/>
+      <c r="M52" s="22"/>
+      <c r="N52" s="22"/>
+      <c r="O52" s="22"/>
+      <c r="P52" s="22"/>
+      <c r="Q52" s="22"/>
+      <c r="R52" s="22"/>
+      <c r="S52" s="22"/>
+      <c r="T52" s="22"/>
+      <c r="U52" s="22"/>
+      <c r="V52" s="22"/>
+      <c r="W52" s="22"/>
+    </row>
+    <row r="53" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="49"/>
+      <c r="B53" s="21"/>
+      <c r="C53" s="23"/>
+      <c r="D53" s="41"/>
+      <c r="E53" s="41"/>
+      <c r="F53" s="18"/>
+      <c r="G53" s="17"/>
+      <c r="H53" s="19"/>
+      <c r="I53" s="20"/>
+      <c r="J53" s="22"/>
+      <c r="K53" s="22"/>
+      <c r="L53" s="22"/>
+      <c r="M53" s="22"/>
+      <c r="N53" s="22"/>
+      <c r="O53" s="22"/>
+      <c r="P53" s="22"/>
+      <c r="Q53" s="22"/>
+      <c r="R53" s="22"/>
+      <c r="S53" s="22"/>
+      <c r="T53" s="22"/>
+      <c r="U53" s="22"/>
+      <c r="V53" s="22"/>
+      <c r="W53" s="22"/>
+    </row>
+    <row r="54" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="49"/>
+      <c r="B54" s="21"/>
+      <c r="C54" s="23"/>
+      <c r="D54" s="41"/>
+      <c r="E54" s="41"/>
+      <c r="F54" s="18"/>
+      <c r="G54" s="17"/>
+      <c r="H54" s="19"/>
+      <c r="I54" s="20"/>
+      <c r="J54" s="22"/>
+      <c r="K54" s="22"/>
+      <c r="L54" s="22"/>
+      <c r="M54" s="22"/>
+      <c r="N54" s="22"/>
+      <c r="O54" s="22"/>
+      <c r="P54" s="22"/>
+      <c r="Q54" s="22"/>
+      <c r="R54" s="22"/>
+      <c r="S54" s="22"/>
+      <c r="T54" s="22"/>
+      <c r="U54" s="22"/>
+      <c r="V54" s="22"/>
+      <c r="W54" s="22"/>
+    </row>
+    <row r="55" spans="1:23" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="49"/>
+      <c r="B55" s="21"/>
+      <c r="C55" s="23" t="s">
         <v>159</v>
       </c>
-      <c r="D43" s="42"/>
-      <c r="E43" s="42"/>
-      <c r="F43" s="19"/>
-      <c r="G43" s="18"/>
-      <c r="H43" s="20"/>
-      <c r="I43" s="21"/>
-      <c r="J43" s="23"/>
-      <c r="K43" s="23"/>
-      <c r="L43" s="23"/>
-      <c r="M43" s="23"/>
-      <c r="N43" s="23"/>
-      <c r="O43" s="23"/>
-      <c r="P43" s="23"/>
-      <c r="Q43" s="23"/>
-      <c r="R43" s="23"/>
-      <c r="S43" s="23"/>
-      <c r="T43" s="23"/>
-      <c r="U43" s="23"/>
-      <c r="V43" s="23"/>
-      <c r="W43" s="23"/>
-    </row>
-    <row r="44" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="50"/>
-      <c r="B44" s="22"/>
-      <c r="C44" s="24"/>
-      <c r="D44" s="42"/>
-      <c r="E44" s="42"/>
-      <c r="F44" s="19"/>
-      <c r="G44" s="18"/>
-      <c r="H44" s="20"/>
-      <c r="I44" s="21"/>
-      <c r="J44" s="23"/>
-      <c r="K44" s="23"/>
-      <c r="L44" s="23"/>
-      <c r="M44" s="23"/>
-      <c r="N44" s="23"/>
-      <c r="O44" s="23"/>
-      <c r="P44" s="23"/>
-      <c r="Q44" s="23"/>
-      <c r="R44" s="23"/>
-      <c r="S44" s="23"/>
-      <c r="T44" s="23"/>
-      <c r="U44" s="23"/>
-      <c r="V44" s="23"/>
-      <c r="W44" s="23"/>
-    </row>
-    <row r="45" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="50"/>
-      <c r="B45" s="22"/>
-      <c r="C45" s="24"/>
-      <c r="D45" s="42"/>
-      <c r="E45" s="42"/>
-      <c r="F45" s="19"/>
-      <c r="G45" s="18"/>
-      <c r="H45" s="20"/>
-      <c r="I45" s="21"/>
-      <c r="J45" s="23"/>
-      <c r="K45" s="23"/>
-      <c r="L45" s="23"/>
-      <c r="M45" s="23"/>
-      <c r="N45" s="23"/>
-      <c r="O45" s="23"/>
-      <c r="P45" s="23"/>
-      <c r="Q45" s="23"/>
-      <c r="R45" s="23"/>
-      <c r="S45" s="23"/>
-      <c r="T45" s="23"/>
-      <c r="U45" s="23"/>
-      <c r="V45" s="23"/>
-      <c r="W45" s="23"/>
-    </row>
-    <row r="46" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="50"/>
-      <c r="B46" s="22"/>
-      <c r="C46" s="24"/>
-      <c r="D46" s="42"/>
-      <c r="E46" s="42"/>
-      <c r="F46" s="19"/>
-      <c r="G46" s="18"/>
-      <c r="H46" s="20"/>
-      <c r="I46" s="21"/>
-      <c r="J46" s="23"/>
-      <c r="K46" s="23"/>
-      <c r="L46" s="23"/>
-      <c r="M46" s="23"/>
-      <c r="N46" s="23"/>
-      <c r="O46" s="23"/>
-      <c r="P46" s="23"/>
-      <c r="Q46" s="23"/>
-      <c r="R46" s="23"/>
-      <c r="S46" s="23"/>
-      <c r="T46" s="23"/>
-      <c r="U46" s="23"/>
-      <c r="V46" s="23"/>
-      <c r="W46" s="23"/>
-    </row>
-    <row r="47" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="50"/>
-      <c r="B47" s="22"/>
-      <c r="C47" s="24"/>
-      <c r="D47" s="42"/>
-      <c r="E47" s="42"/>
-      <c r="F47" s="19"/>
-      <c r="G47" s="18"/>
-      <c r="H47" s="20"/>
-      <c r="I47" s="21"/>
-      <c r="J47" s="23"/>
-      <c r="K47" s="23"/>
-      <c r="L47" s="23"/>
-      <c r="M47" s="23"/>
-      <c r="N47" s="23"/>
-      <c r="O47" s="23"/>
-      <c r="P47" s="23"/>
-      <c r="Q47" s="23"/>
-      <c r="R47" s="23"/>
-      <c r="S47" s="23"/>
-      <c r="T47" s="23"/>
-      <c r="U47" s="23"/>
-      <c r="V47" s="23"/>
-      <c r="W47" s="23"/>
-    </row>
-    <row r="48" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="50"/>
-      <c r="B48" s="22"/>
-      <c r="C48" s="24" t="s">
+      <c r="D55" s="41"/>
+      <c r="E55" s="41"/>
+      <c r="F55" s="18"/>
+      <c r="G55" s="17"/>
+      <c r="H55" s="19"/>
+      <c r="I55" s="20"/>
+      <c r="J55" s="22"/>
+      <c r="K55" s="22"/>
+      <c r="L55" s="22"/>
+      <c r="M55" s="22"/>
+      <c r="N55" s="22"/>
+      <c r="O55" s="22"/>
+      <c r="P55" s="22"/>
+      <c r="Q55" s="22"/>
+      <c r="R55" s="22"/>
+      <c r="S55" s="22"/>
+      <c r="T55" s="22"/>
+      <c r="U55" s="22"/>
+      <c r="V55" s="22"/>
+      <c r="W55" s="22"/>
+    </row>
+    <row r="56" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="49"/>
+      <c r="B56" s="21"/>
+      <c r="C56" s="23" t="s">
         <v>159</v>
       </c>
-      <c r="D48" s="42"/>
-      <c r="E48" s="42"/>
-      <c r="F48" s="19"/>
-      <c r="G48" s="18"/>
-      <c r="H48" s="20"/>
-      <c r="I48" s="21"/>
-      <c r="J48" s="23"/>
-      <c r="K48" s="23"/>
-      <c r="L48" s="23"/>
-      <c r="M48" s="23"/>
-      <c r="N48" s="23"/>
-      <c r="O48" s="23"/>
-      <c r="P48" s="23"/>
-      <c r="Q48" s="23"/>
-      <c r="R48" s="23"/>
-      <c r="S48" s="23"/>
-      <c r="T48" s="23"/>
-      <c r="U48" s="23"/>
-      <c r="V48" s="23"/>
-      <c r="W48" s="23"/>
-    </row>
-    <row r="49" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="50"/>
-      <c r="B49" s="22"/>
-      <c r="C49" s="24" t="s">
+      <c r="D56" s="41"/>
+      <c r="E56" s="41"/>
+      <c r="F56" s="18"/>
+      <c r="G56" s="17"/>
+      <c r="H56" s="19"/>
+      <c r="I56" s="20"/>
+      <c r="J56" s="22"/>
+      <c r="K56" s="22"/>
+      <c r="L56" s="22"/>
+      <c r="M56" s="22"/>
+      <c r="N56" s="22"/>
+      <c r="O56" s="22"/>
+      <c r="P56" s="22"/>
+      <c r="Q56" s="22"/>
+      <c r="R56" s="22"/>
+      <c r="S56" s="22"/>
+      <c r="T56" s="22"/>
+      <c r="U56" s="22"/>
+      <c r="V56" s="22"/>
+      <c r="W56" s="22"/>
+    </row>
+    <row r="57" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="49"/>
+      <c r="B57" s="21"/>
+      <c r="C57" s="23" t="s">
         <v>159</v>
       </c>
-      <c r="D49" s="42"/>
-      <c r="E49" s="42"/>
-      <c r="F49" s="19"/>
-      <c r="G49" s="18"/>
-      <c r="H49" s="20"/>
-      <c r="I49" s="21"/>
-      <c r="J49" s="23"/>
-      <c r="K49" s="23"/>
-      <c r="L49" s="23"/>
-      <c r="M49" s="23"/>
-      <c r="N49" s="23"/>
-      <c r="O49" s="23"/>
-      <c r="P49" s="23"/>
-      <c r="Q49" s="23"/>
-      <c r="R49" s="23"/>
-      <c r="S49" s="23"/>
-      <c r="T49" s="23"/>
-      <c r="U49" s="23"/>
-      <c r="V49" s="23"/>
-      <c r="W49" s="23"/>
-    </row>
-    <row r="50" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="50"/>
-      <c r="B50" s="22"/>
-      <c r="C50" s="24" t="s">
+      <c r="D57" s="41"/>
+      <c r="E57" s="41"/>
+      <c r="F57" s="18"/>
+      <c r="G57" s="17"/>
+      <c r="H57" s="19"/>
+      <c r="I57" s="20"/>
+      <c r="J57" s="22"/>
+      <c r="K57" s="22"/>
+      <c r="L57" s="22"/>
+      <c r="M57" s="22"/>
+      <c r="N57" s="22"/>
+      <c r="O57" s="22"/>
+      <c r="P57" s="22"/>
+      <c r="Q57" s="22"/>
+      <c r="R57" s="22"/>
+      <c r="S57" s="22"/>
+      <c r="T57" s="22"/>
+      <c r="U57" s="22"/>
+      <c r="V57" s="22"/>
+      <c r="W57" s="22"/>
+    </row>
+    <row r="58" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="49"/>
+      <c r="B58" s="21"/>
+      <c r="C58" s="23"/>
+      <c r="D58" s="41"/>
+      <c r="E58" s="41"/>
+      <c r="F58" s="18"/>
+      <c r="G58" s="17"/>
+      <c r="H58" s="19"/>
+      <c r="I58" s="20"/>
+      <c r="J58" s="22"/>
+      <c r="K58" s="22"/>
+      <c r="L58" s="22"/>
+      <c r="M58" s="22"/>
+      <c r="N58" s="22"/>
+      <c r="O58" s="22"/>
+      <c r="P58" s="22"/>
+      <c r="Q58" s="22"/>
+      <c r="R58" s="22"/>
+      <c r="S58" s="22"/>
+      <c r="T58" s="22"/>
+      <c r="U58" s="22"/>
+      <c r="V58" s="22"/>
+      <c r="W58" s="22"/>
+    </row>
+    <row r="59" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="49"/>
+      <c r="B59" s="21"/>
+      <c r="C59" s="23"/>
+      <c r="D59" s="41"/>
+      <c r="E59" s="41"/>
+      <c r="F59" s="18"/>
+      <c r="G59" s="17"/>
+      <c r="H59" s="19"/>
+      <c r="I59" s="20"/>
+      <c r="J59" s="22"/>
+      <c r="K59" s="22"/>
+      <c r="L59" s="22"/>
+      <c r="M59" s="22"/>
+      <c r="N59" s="22"/>
+      <c r="O59" s="22"/>
+      <c r="P59" s="22"/>
+      <c r="Q59" s="22"/>
+      <c r="R59" s="22"/>
+      <c r="S59" s="22"/>
+      <c r="T59" s="22"/>
+      <c r="U59" s="22"/>
+      <c r="V59" s="22"/>
+      <c r="W59" s="22"/>
+    </row>
+    <row r="60" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="49"/>
+      <c r="B60" s="21"/>
+      <c r="C60" s="23"/>
+      <c r="D60" s="41"/>
+      <c r="E60" s="41"/>
+      <c r="F60" s="18"/>
+      <c r="G60" s="17"/>
+      <c r="H60" s="19"/>
+      <c r="I60" s="20"/>
+      <c r="J60" s="22"/>
+      <c r="K60" s="22"/>
+      <c r="L60" s="22"/>
+      <c r="M60" s="22"/>
+      <c r="N60" s="22"/>
+      <c r="O60" s="22"/>
+      <c r="P60" s="22"/>
+      <c r="Q60" s="22"/>
+      <c r="R60" s="22"/>
+      <c r="S60" s="22"/>
+      <c r="T60" s="22"/>
+      <c r="U60" s="22"/>
+      <c r="V60" s="22"/>
+      <c r="W60" s="22"/>
+    </row>
+    <row r="61" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="49"/>
+      <c r="B61" s="21"/>
+      <c r="C61" s="23"/>
+      <c r="D61" s="41"/>
+      <c r="E61" s="41"/>
+      <c r="F61" s="18"/>
+      <c r="G61" s="17"/>
+      <c r="H61" s="19"/>
+      <c r="I61" s="20"/>
+      <c r="J61" s="22"/>
+      <c r="K61" s="22"/>
+      <c r="L61" s="22"/>
+      <c r="M61" s="22"/>
+      <c r="N61" s="22"/>
+      <c r="O61" s="22"/>
+      <c r="P61" s="22"/>
+      <c r="Q61" s="22"/>
+      <c r="R61" s="22"/>
+      <c r="S61" s="22"/>
+      <c r="T61" s="22"/>
+      <c r="U61" s="22"/>
+      <c r="V61" s="22"/>
+      <c r="W61" s="22"/>
+    </row>
+    <row r="62" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="49"/>
+      <c r="B62" s="21"/>
+      <c r="C62" s="23" t="s">
         <v>159</v>
       </c>
-      <c r="D50" s="42"/>
-      <c r="E50" s="42"/>
-      <c r="F50" s="19"/>
-      <c r="G50" s="18"/>
-      <c r="H50" s="20"/>
-      <c r="I50" s="21"/>
-      <c r="J50" s="23"/>
-      <c r="K50" s="23"/>
-      <c r="L50" s="23"/>
-      <c r="M50" s="23"/>
-      <c r="N50" s="23"/>
-      <c r="O50" s="23"/>
-      <c r="P50" s="23"/>
-      <c r="Q50" s="23"/>
-      <c r="R50" s="23"/>
-      <c r="S50" s="23"/>
-      <c r="T50" s="23"/>
-      <c r="U50" s="23"/>
-      <c r="V50" s="23"/>
-      <c r="W50" s="23"/>
-    </row>
-    <row r="51" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="50"/>
-      <c r="B51" s="22"/>
-      <c r="C51" s="24"/>
-      <c r="D51" s="42"/>
-      <c r="E51" s="42"/>
-      <c r="F51" s="19"/>
-      <c r="G51" s="18"/>
-      <c r="H51" s="20"/>
-      <c r="I51" s="21"/>
-      <c r="J51" s="23"/>
-      <c r="K51" s="23"/>
-      <c r="L51" s="23"/>
-      <c r="M51" s="23"/>
-      <c r="N51" s="23"/>
-      <c r="O51" s="23"/>
-      <c r="P51" s="23"/>
-      <c r="Q51" s="23"/>
-      <c r="R51" s="23"/>
-      <c r="S51" s="23"/>
-      <c r="T51" s="23"/>
-      <c r="U51" s="23"/>
-      <c r="V51" s="23"/>
-      <c r="W51" s="23"/>
-    </row>
-    <row r="52" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="50"/>
-      <c r="B52" s="22"/>
-      <c r="C52" s="24"/>
-      <c r="D52" s="42"/>
-      <c r="E52" s="42"/>
-      <c r="F52" s="19"/>
-      <c r="G52" s="18"/>
-      <c r="H52" s="20"/>
-      <c r="I52" s="21"/>
-      <c r="J52" s="23"/>
-      <c r="K52" s="23"/>
-      <c r="L52" s="23"/>
-      <c r="M52" s="23"/>
-      <c r="N52" s="23"/>
-      <c r="O52" s="23"/>
-      <c r="P52" s="23"/>
-      <c r="Q52" s="23"/>
-      <c r="R52" s="23"/>
-      <c r="S52" s="23"/>
-      <c r="T52" s="23"/>
-      <c r="U52" s="23"/>
-      <c r="V52" s="23"/>
-      <c r="W52" s="23"/>
-    </row>
-    <row r="53" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="50"/>
-      <c r="B53" s="22"/>
-      <c r="C53" s="24"/>
-      <c r="D53" s="42"/>
-      <c r="E53" s="42"/>
-      <c r="F53" s="19"/>
-      <c r="G53" s="18"/>
-      <c r="H53" s="20"/>
-      <c r="I53" s="21"/>
-      <c r="J53" s="23"/>
-      <c r="K53" s="23"/>
-      <c r="L53" s="23"/>
-      <c r="M53" s="23"/>
-      <c r="N53" s="23"/>
-      <c r="O53" s="23"/>
-      <c r="P53" s="23"/>
-      <c r="Q53" s="23"/>
-      <c r="R53" s="23"/>
-      <c r="S53" s="23"/>
-      <c r="T53" s="23"/>
-      <c r="U53" s="23"/>
-      <c r="V53" s="23"/>
-      <c r="W53" s="23"/>
-    </row>
-    <row r="54" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="50"/>
-      <c r="B54" s="22"/>
-      <c r="C54" s="24"/>
-      <c r="D54" s="42"/>
-      <c r="E54" s="42"/>
-      <c r="F54" s="19"/>
-      <c r="G54" s="18"/>
-      <c r="H54" s="20"/>
-      <c r="I54" s="21"/>
-      <c r="J54" s="23"/>
-      <c r="K54" s="23"/>
-      <c r="L54" s="23"/>
-      <c r="M54" s="23"/>
-      <c r="N54" s="23"/>
-      <c r="O54" s="23"/>
-      <c r="P54" s="23"/>
-      <c r="Q54" s="23"/>
-      <c r="R54" s="23"/>
-      <c r="S54" s="23"/>
-      <c r="T54" s="23"/>
-      <c r="U54" s="23"/>
-      <c r="V54" s="23"/>
-      <c r="W54" s="23"/>
-    </row>
-    <row r="55" spans="1:23" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="50"/>
-      <c r="B55" s="22"/>
-      <c r="C55" s="24" t="s">
+      <c r="D62" s="41"/>
+      <c r="E62" s="41"/>
+      <c r="F62" s="18"/>
+      <c r="G62" s="17"/>
+      <c r="H62" s="19"/>
+      <c r="I62" s="20"/>
+      <c r="J62" s="22"/>
+      <c r="K62" s="22"/>
+      <c r="L62" s="22"/>
+      <c r="M62" s="22"/>
+      <c r="N62" s="22"/>
+      <c r="O62" s="22"/>
+      <c r="P62" s="22"/>
+      <c r="Q62" s="22"/>
+      <c r="R62" s="22"/>
+      <c r="S62" s="22"/>
+      <c r="T62" s="22"/>
+      <c r="U62" s="22"/>
+      <c r="V62" s="22"/>
+      <c r="W62" s="22"/>
+    </row>
+    <row r="63" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="49"/>
+      <c r="B63" s="21"/>
+      <c r="C63" s="23" t="s">
         <v>159</v>
       </c>
-      <c r="D55" s="42"/>
-      <c r="E55" s="42"/>
-      <c r="F55" s="19"/>
-      <c r="G55" s="18"/>
-      <c r="H55" s="20"/>
-      <c r="I55" s="21"/>
-      <c r="J55" s="23"/>
-      <c r="K55" s="23"/>
-      <c r="L55" s="23"/>
-      <c r="M55" s="23"/>
-      <c r="N55" s="23"/>
-      <c r="O55" s="23"/>
-      <c r="P55" s="23"/>
-      <c r="Q55" s="23"/>
-      <c r="R55" s="23"/>
-      <c r="S55" s="23"/>
-      <c r="T55" s="23"/>
-      <c r="U55" s="23"/>
-      <c r="V55" s="23"/>
-      <c r="W55" s="23"/>
-    </row>
-    <row r="56" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="50"/>
-      <c r="B56" s="22"/>
-      <c r="C56" s="24" t="s">
+      <c r="D63" s="41"/>
+      <c r="E63" s="41"/>
+      <c r="F63" s="18"/>
+      <c r="G63" s="17"/>
+      <c r="H63" s="19"/>
+      <c r="I63" s="20"/>
+      <c r="J63" s="22"/>
+      <c r="K63" s="22"/>
+      <c r="L63" s="22"/>
+      <c r="M63" s="22"/>
+      <c r="N63" s="22"/>
+      <c r="O63" s="22"/>
+      <c r="P63" s="22"/>
+      <c r="Q63" s="22"/>
+      <c r="R63" s="22"/>
+      <c r="S63" s="22"/>
+      <c r="T63" s="22"/>
+      <c r="U63" s="22"/>
+      <c r="V63" s="22"/>
+      <c r="W63" s="22"/>
+    </row>
+    <row r="64" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="49"/>
+      <c r="B64" s="21"/>
+      <c r="C64" s="23"/>
+      <c r="D64" s="41"/>
+      <c r="E64" s="41"/>
+      <c r="F64" s="18"/>
+      <c r="G64" s="17"/>
+      <c r="H64" s="19"/>
+      <c r="I64" s="20"/>
+      <c r="J64" s="22"/>
+      <c r="K64" s="22"/>
+      <c r="L64" s="22"/>
+      <c r="M64" s="22"/>
+      <c r="N64" s="22"/>
+      <c r="O64" s="22"/>
+      <c r="P64" s="22"/>
+      <c r="Q64" s="22"/>
+      <c r="R64" s="22"/>
+      <c r="S64" s="22"/>
+      <c r="T64" s="22"/>
+      <c r="U64" s="22"/>
+      <c r="V64" s="22"/>
+      <c r="W64" s="22"/>
+    </row>
+    <row r="65" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="49"/>
+      <c r="B65" s="21"/>
+      <c r="C65" s="23"/>
+      <c r="D65" s="41"/>
+      <c r="E65" s="41"/>
+      <c r="F65" s="18"/>
+      <c r="G65" s="17"/>
+      <c r="H65" s="19"/>
+      <c r="I65" s="20"/>
+      <c r="J65" s="22"/>
+      <c r="K65" s="22"/>
+      <c r="L65" s="22"/>
+      <c r="M65" s="22"/>
+      <c r="N65" s="22"/>
+      <c r="O65" s="22"/>
+      <c r="P65" s="22"/>
+      <c r="Q65" s="22"/>
+      <c r="R65" s="22"/>
+      <c r="S65" s="22"/>
+      <c r="T65" s="22"/>
+      <c r="U65" s="22"/>
+      <c r="V65" s="22"/>
+      <c r="W65" s="22"/>
+    </row>
+    <row r="66" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="49"/>
+      <c r="B66" s="21"/>
+      <c r="C66" s="23"/>
+      <c r="D66" s="41"/>
+      <c r="E66" s="41"/>
+      <c r="F66" s="18"/>
+      <c r="G66" s="17"/>
+      <c r="H66" s="19"/>
+      <c r="I66" s="20"/>
+      <c r="J66" s="22"/>
+      <c r="K66" s="22"/>
+      <c r="L66" s="22"/>
+      <c r="M66" s="22"/>
+      <c r="N66" s="22"/>
+      <c r="O66" s="22"/>
+      <c r="P66" s="22"/>
+      <c r="Q66" s="22"/>
+      <c r="R66" s="22"/>
+      <c r="S66" s="22"/>
+      <c r="T66" s="22"/>
+      <c r="U66" s="22"/>
+      <c r="V66" s="22"/>
+      <c r="W66" s="22"/>
+    </row>
+    <row r="67" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="49"/>
+      <c r="B67" s="21"/>
+      <c r="C67" s="23" t="s">
         <v>159</v>
       </c>
-      <c r="D56" s="42"/>
-      <c r="E56" s="42"/>
-      <c r="F56" s="19"/>
-      <c r="G56" s="18"/>
-      <c r="H56" s="20"/>
-      <c r="I56" s="21"/>
-      <c r="J56" s="23"/>
-      <c r="K56" s="23"/>
-      <c r="L56" s="23"/>
-      <c r="M56" s="23"/>
-      <c r="N56" s="23"/>
-      <c r="O56" s="23"/>
-      <c r="P56" s="23"/>
-      <c r="Q56" s="23"/>
-      <c r="R56" s="23"/>
-      <c r="S56" s="23"/>
-      <c r="T56" s="23"/>
-      <c r="U56" s="23"/>
-      <c r="V56" s="23"/>
-      <c r="W56" s="23"/>
-    </row>
-    <row r="57" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="50"/>
-      <c r="B57" s="22"/>
-      <c r="C57" s="24" t="s">
+      <c r="D67" s="41"/>
+      <c r="E67" s="41"/>
+      <c r="F67" s="18"/>
+      <c r="G67" s="17"/>
+      <c r="H67" s="19"/>
+      <c r="I67" s="20"/>
+      <c r="J67" s="22"/>
+      <c r="K67" s="22"/>
+      <c r="L67" s="22"/>
+      <c r="M67" s="22"/>
+      <c r="N67" s="22"/>
+      <c r="O67" s="22"/>
+      <c r="P67" s="22"/>
+      <c r="Q67" s="22"/>
+      <c r="R67" s="22"/>
+      <c r="S67" s="22"/>
+      <c r="T67" s="22"/>
+      <c r="U67" s="22"/>
+      <c r="V67" s="22"/>
+      <c r="W67" s="22"/>
+    </row>
+    <row r="68" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="49"/>
+      <c r="B68" s="21"/>
+      <c r="C68" s="23"/>
+      <c r="D68" s="41"/>
+      <c r="E68" s="41"/>
+      <c r="F68" s="18"/>
+      <c r="G68" s="17"/>
+      <c r="H68" s="19"/>
+      <c r="I68" s="20"/>
+      <c r="J68" s="22"/>
+      <c r="K68" s="22"/>
+      <c r="L68" s="22"/>
+      <c r="M68" s="22"/>
+      <c r="N68" s="22"/>
+      <c r="O68" s="22"/>
+      <c r="P68" s="22"/>
+      <c r="Q68" s="22"/>
+      <c r="R68" s="22"/>
+      <c r="S68" s="22"/>
+      <c r="T68" s="22"/>
+      <c r="U68" s="22"/>
+      <c r="V68" s="22"/>
+      <c r="W68" s="22"/>
+    </row>
+    <row r="69" spans="1:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="49"/>
+      <c r="B69" s="21"/>
+      <c r="C69" s="23" t="s">
         <v>159</v>
       </c>
-      <c r="D57" s="42"/>
-      <c r="E57" s="42"/>
-      <c r="F57" s="19"/>
-      <c r="G57" s="18"/>
-      <c r="H57" s="20"/>
-      <c r="I57" s="21"/>
-      <c r="J57" s="23"/>
-      <c r="K57" s="23"/>
-      <c r="L57" s="23"/>
-      <c r="M57" s="23"/>
-      <c r="N57" s="23"/>
-      <c r="O57" s="23"/>
-      <c r="P57" s="23"/>
-      <c r="Q57" s="23"/>
-      <c r="R57" s="23"/>
-      <c r="S57" s="23"/>
-      <c r="T57" s="23"/>
-      <c r="U57" s="23"/>
-      <c r="V57" s="23"/>
-      <c r="W57" s="23"/>
-    </row>
-    <row r="58" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="50"/>
-      <c r="B58" s="22"/>
-      <c r="C58" s="24"/>
-      <c r="D58" s="42"/>
-      <c r="E58" s="42"/>
-      <c r="F58" s="19"/>
-      <c r="G58" s="18"/>
-      <c r="H58" s="20"/>
-      <c r="I58" s="21"/>
-      <c r="J58" s="23"/>
-      <c r="K58" s="23"/>
-      <c r="L58" s="23"/>
-      <c r="M58" s="23"/>
-      <c r="N58" s="23"/>
-      <c r="O58" s="23"/>
-      <c r="P58" s="23"/>
-      <c r="Q58" s="23"/>
-      <c r="R58" s="23"/>
-      <c r="S58" s="23"/>
-      <c r="T58" s="23"/>
-      <c r="U58" s="23"/>
-      <c r="V58" s="23"/>
-      <c r="W58" s="23"/>
-    </row>
-    <row r="59" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="50"/>
-      <c r="B59" s="22"/>
-      <c r="C59" s="24"/>
-      <c r="D59" s="42"/>
-      <c r="E59" s="42"/>
-      <c r="F59" s="19"/>
-      <c r="G59" s="18"/>
-      <c r="H59" s="20"/>
-      <c r="I59" s="21"/>
-      <c r="J59" s="23"/>
-      <c r="K59" s="23"/>
-      <c r="L59" s="23"/>
-      <c r="M59" s="23"/>
-      <c r="N59" s="23"/>
-      <c r="O59" s="23"/>
-      <c r="P59" s="23"/>
-      <c r="Q59" s="23"/>
-      <c r="R59" s="23"/>
-      <c r="S59" s="23"/>
-      <c r="T59" s="23"/>
-      <c r="U59" s="23"/>
-      <c r="V59" s="23"/>
-      <c r="W59" s="23"/>
-    </row>
-    <row r="60" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="50"/>
-      <c r="B60" s="22"/>
-      <c r="C60" s="24"/>
-      <c r="D60" s="42"/>
-      <c r="E60" s="42"/>
-      <c r="F60" s="19"/>
-      <c r="G60" s="18"/>
-      <c r="H60" s="20"/>
-      <c r="I60" s="21"/>
-      <c r="J60" s="23"/>
-      <c r="K60" s="23"/>
-      <c r="L60" s="23"/>
-      <c r="M60" s="23"/>
-      <c r="N60" s="23"/>
-      <c r="O60" s="23"/>
-      <c r="P60" s="23"/>
-      <c r="Q60" s="23"/>
-      <c r="R60" s="23"/>
-      <c r="S60" s="23"/>
-      <c r="T60" s="23"/>
-      <c r="U60" s="23"/>
-      <c r="V60" s="23"/>
-      <c r="W60" s="23"/>
-    </row>
-    <row r="61" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="50"/>
-      <c r="B61" s="22"/>
-      <c r="C61" s="24"/>
-      <c r="D61" s="42"/>
-      <c r="E61" s="42"/>
-      <c r="F61" s="19"/>
-      <c r="G61" s="18"/>
-      <c r="H61" s="20"/>
-      <c r="I61" s="21"/>
-      <c r="J61" s="23"/>
-      <c r="K61" s="23"/>
-      <c r="L61" s="23"/>
-      <c r="M61" s="23"/>
-      <c r="N61" s="23"/>
-      <c r="O61" s="23"/>
-      <c r="P61" s="23"/>
-      <c r="Q61" s="23"/>
-      <c r="R61" s="23"/>
-      <c r="S61" s="23"/>
-      <c r="T61" s="23"/>
-      <c r="U61" s="23"/>
-      <c r="V61" s="23"/>
-      <c r="W61" s="23"/>
-    </row>
-    <row r="62" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="50"/>
-      <c r="B62" s="22"/>
-      <c r="C62" s="24" t="s">
-        <v>159</v>
-      </c>
-      <c r="D62" s="42"/>
-      <c r="E62" s="42"/>
-      <c r="F62" s="19"/>
-      <c r="G62" s="18"/>
-      <c r="H62" s="20"/>
-      <c r="I62" s="21"/>
-      <c r="J62" s="23"/>
-      <c r="K62" s="23"/>
-      <c r="L62" s="23"/>
-      <c r="M62" s="23"/>
-      <c r="N62" s="23"/>
-      <c r="O62" s="23"/>
-      <c r="P62" s="23"/>
-      <c r="Q62" s="23"/>
-      <c r="R62" s="23"/>
-      <c r="S62" s="23"/>
-      <c r="T62" s="23"/>
-      <c r="U62" s="23"/>
-      <c r="V62" s="23"/>
-      <c r="W62" s="23"/>
-    </row>
-    <row r="63" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="50"/>
-      <c r="B63" s="22"/>
-      <c r="C63" s="24" t="s">
-        <v>159</v>
-      </c>
-      <c r="D63" s="42"/>
-      <c r="E63" s="42"/>
-      <c r="F63" s="19"/>
-      <c r="G63" s="18"/>
-      <c r="H63" s="20"/>
-      <c r="I63" s="21"/>
-      <c r="J63" s="23"/>
-      <c r="K63" s="23"/>
-      <c r="L63" s="23"/>
-      <c r="M63" s="23"/>
-      <c r="N63" s="23"/>
-      <c r="O63" s="23"/>
-      <c r="P63" s="23"/>
-      <c r="Q63" s="23"/>
-      <c r="R63" s="23"/>
-      <c r="S63" s="23"/>
-      <c r="T63" s="23"/>
-      <c r="U63" s="23"/>
-      <c r="V63" s="23"/>
-      <c r="W63" s="23"/>
-    </row>
-    <row r="64" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="50"/>
-      <c r="B64" s="22"/>
-      <c r="C64" s="24"/>
-      <c r="D64" s="42"/>
-      <c r="E64" s="42"/>
-      <c r="F64" s="19"/>
-      <c r="G64" s="18"/>
-      <c r="H64" s="20"/>
-      <c r="I64" s="21"/>
-      <c r="J64" s="23"/>
-      <c r="K64" s="23"/>
-      <c r="L64" s="23"/>
-      <c r="M64" s="23"/>
-      <c r="N64" s="23"/>
-      <c r="O64" s="23"/>
-      <c r="P64" s="23"/>
-      <c r="Q64" s="23"/>
-      <c r="R64" s="23"/>
-      <c r="S64" s="23"/>
-      <c r="T64" s="23"/>
-      <c r="U64" s="23"/>
-      <c r="V64" s="23"/>
-      <c r="W64" s="23"/>
-    </row>
-    <row r="65" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="50"/>
-      <c r="B65" s="22"/>
-      <c r="C65" s="24"/>
-      <c r="D65" s="42"/>
-      <c r="E65" s="42"/>
-      <c r="F65" s="19"/>
-      <c r="G65" s="18"/>
-      <c r="H65" s="20"/>
-      <c r="I65" s="21"/>
-      <c r="J65" s="23"/>
-      <c r="K65" s="23"/>
-      <c r="L65" s="23"/>
-      <c r="M65" s="23"/>
-      <c r="N65" s="23"/>
-      <c r="O65" s="23"/>
-      <c r="P65" s="23"/>
-      <c r="Q65" s="23"/>
-      <c r="R65" s="23"/>
-      <c r="S65" s="23"/>
-      <c r="T65" s="23"/>
-      <c r="U65" s="23"/>
-      <c r="V65" s="23"/>
-      <c r="W65" s="23"/>
-    </row>
-    <row r="66" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="50"/>
-      <c r="B66" s="22"/>
-      <c r="C66" s="24"/>
-      <c r="D66" s="42"/>
-      <c r="E66" s="42"/>
-      <c r="F66" s="19"/>
-      <c r="G66" s="18"/>
-      <c r="H66" s="20"/>
-      <c r="I66" s="21"/>
-      <c r="J66" s="23"/>
-      <c r="K66" s="23"/>
-      <c r="L66" s="23"/>
-      <c r="M66" s="23"/>
-      <c r="N66" s="23"/>
-      <c r="O66" s="23"/>
-      <c r="P66" s="23"/>
-      <c r="Q66" s="23"/>
-      <c r="R66" s="23"/>
-      <c r="S66" s="23"/>
-      <c r="T66" s="23"/>
-      <c r="U66" s="23"/>
-      <c r="V66" s="23"/>
-      <c r="W66" s="23"/>
-    </row>
-    <row r="67" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="50"/>
-      <c r="B67" s="22"/>
-      <c r="C67" s="24" t="s">
-        <v>159</v>
-      </c>
-      <c r="D67" s="42"/>
-      <c r="E67" s="42"/>
-      <c r="F67" s="19"/>
-      <c r="G67" s="18"/>
-      <c r="H67" s="20"/>
-      <c r="I67" s="21"/>
-      <c r="J67" s="23"/>
-      <c r="K67" s="23"/>
-      <c r="L67" s="23"/>
-      <c r="M67" s="23"/>
-      <c r="N67" s="23"/>
-      <c r="O67" s="23"/>
-      <c r="P67" s="23"/>
-      <c r="Q67" s="23"/>
-      <c r="R67" s="23"/>
-      <c r="S67" s="23"/>
-      <c r="T67" s="23"/>
-      <c r="U67" s="23"/>
-      <c r="V67" s="23"/>
-      <c r="W67" s="23"/>
-    </row>
-    <row r="68" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="50"/>
-      <c r="B68" s="22"/>
-      <c r="C68" s="24"/>
-      <c r="D68" s="42"/>
-      <c r="E68" s="42"/>
-      <c r="F68" s="19"/>
-      <c r="G68" s="18"/>
-      <c r="H68" s="20"/>
-      <c r="I68" s="21"/>
-      <c r="J68" s="23"/>
-      <c r="K68" s="23"/>
-      <c r="L68" s="23"/>
-      <c r="M68" s="23"/>
-      <c r="N68" s="23"/>
-      <c r="O68" s="23"/>
-      <c r="P68" s="23"/>
-      <c r="Q68" s="23"/>
-      <c r="R68" s="23"/>
-      <c r="S68" s="23"/>
-      <c r="T68" s="23"/>
-      <c r="U68" s="23"/>
-      <c r="V68" s="23"/>
-      <c r="W68" s="23"/>
-    </row>
-    <row r="69" spans="1:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="50"/>
-      <c r="B69" s="22"/>
-      <c r="C69" s="24" t="s">
-        <v>159</v>
-      </c>
-      <c r="D69" s="42"/>
-      <c r="E69" s="42"/>
-      <c r="F69" s="19"/>
-      <c r="G69" s="18"/>
-      <c r="H69" s="20"/>
-      <c r="I69" s="21"/>
-      <c r="J69" s="23"/>
-      <c r="K69" s="23"/>
-      <c r="L69" s="23"/>
-      <c r="M69" s="23"/>
-      <c r="N69" s="23"/>
-      <c r="O69" s="23"/>
-      <c r="P69" s="23"/>
-      <c r="Q69" s="23"/>
-      <c r="R69" s="23"/>
-      <c r="S69" s="23"/>
-      <c r="T69" s="23"/>
-      <c r="U69" s="23"/>
-      <c r="V69" s="23"/>
-      <c r="W69" s="23"/>
+      <c r="D69" s="41"/>
+      <c r="E69" s="41"/>
+      <c r="F69" s="18"/>
+      <c r="G69" s="17"/>
+      <c r="H69" s="19"/>
+      <c r="I69" s="20"/>
+      <c r="J69" s="22"/>
+      <c r="K69" s="22"/>
+      <c r="L69" s="22"/>
+      <c r="M69" s="22"/>
+      <c r="N69" s="22"/>
+      <c r="O69" s="22"/>
+      <c r="P69" s="22"/>
+      <c r="Q69" s="22"/>
+      <c r="R69" s="22"/>
+      <c r="S69" s="22"/>
+      <c r="T69" s="22"/>
+      <c r="U69" s="22"/>
+      <c r="V69" s="22"/>
+      <c r="W69" s="22"/>
     </row>
     <row r="70" spans="1:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="25"/>
-      <c r="B70" s="26"/>
-      <c r="C70" s="27"/>
-      <c r="D70" s="29"/>
-      <c r="E70" s="29"/>
-      <c r="F70" s="28"/>
-      <c r="G70" s="28"/>
-      <c r="H70" s="29"/>
-      <c r="I70" s="30"/>
-      <c r="J70" s="30"/>
-      <c r="K70" s="30"/>
-      <c r="L70" s="30"/>
+      <c r="A70" s="24"/>
+      <c r="B70" s="25"/>
+      <c r="C70" s="26"/>
+      <c r="D70" s="28"/>
+      <c r="E70" s="28"/>
+      <c r="F70" s="27"/>
+      <c r="G70" s="27"/>
+      <c r="H70" s="28"/>
+      <c r="I70" s="29"/>
+      <c r="J70" s="29"/>
+      <c r="K70" s="29"/>
+      <c r="L70" s="29"/>
     </row>
     <row r="72" spans="1:23" ht="53.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="73" spans="1:23" ht="42" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -5111,14 +5525,14 @@
     <dataValidation type="decimal" operator="lessThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I10:I11 I21:I22 J6:J9 J10:J11 J13:J22 J26:L70 K5 K7:K8 K10:K12 K14:K22 L5:L6 L8 L9 L10:L13 L15:L22 M5:M7 M9 M10:M14 M16:M22 M26:Q69 N5:N8 N10:N15 N17:N22 O5:Q9 O11:O16 O18:O22 P10 P12:P17 P19:P22 Q10:Q18 Q20:Q22 R5:R19 R21:R69 S5:S20 S23:S69 T5:W69" xr:uid="{00000000-0002-0000-0100-000004000000}">
       <formula1>H5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F10:F11 F18 F20 F22 H7:H11 H15 H18 H20 H22:H69" xr:uid="{00000000-0002-0000-0100-000005000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F10:F11 F18 F20 F22 H7:H11 H15 H18 H20 H22:H28 H31 H33 H38:H69" xr:uid="{00000000-0002-0000-0100-000005000000}">
       <formula1>"1- Not Started, 2- In Progress, 3- Completed"</formula1>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I7 I26 I29:I69" xr:uid="{00000000-0002-0000-0100-000006000000}">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I7 I26 I38:I69" xr:uid="{00000000-0002-0000-0100-000006000000}">
       <formula1>0</formula1>
       <formula2>12</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E11 E20 G18 G10 G23 G26 G30:G69" xr:uid="{00000000-0002-0000-0100-000007000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E11 E20 G18 G10 G23 G26 G32 G38:G69" xr:uid="{00000000-0002-0000-0100-000007000000}">
       <formula1>"Build, Coding, Design, Integration Test, Regression Test, System Test, Unit Test, Others"</formula1>
     </dataValidation>
     <dataValidation type="decimal" operator="lessThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I9" xr:uid="{00000000-0002-0000-0100-000008000000}">
@@ -5134,7 +5548,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="41.5546875" customWidth="1"/>
@@ -5143,21 +5557,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="35" t="s">
         <v>160</v>
       </c>
-      <c r="B1" s="36" t="s">
+      <c r="B1" s="35" t="s">
         <v>161</v>
       </c>
-      <c r="C1" s="36" t="s">
+      <c r="C1" s="35" t="s">
         <v>162</v>
       </c>
-      <c r="D1" s="36" t="s">
+      <c r="D1" s="35" t="s">
         <v>163</v>
       </c>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
     </row>
     <row r="2" spans="1:7" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
@@ -5169,12 +5583,12 @@
       <c r="C2" t="s">
         <v>164</v>
       </c>
-      <c r="D2" s="54" t="s">
+      <c r="D2" s="53" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="52" t="s">
+      <c r="A3" s="51" t="s">
         <v>9</v>
       </c>
       <c r="B3" t="s">
@@ -5183,7 +5597,7 @@
       <c r="C3" t="s">
         <v>166</v>
       </c>
-      <c r="D3" s="52" t="s">
+      <c r="D3" s="51" t="s">
         <v>167</v>
       </c>
     </row>
@@ -5194,10 +5608,10 @@
       <c r="B4" t="s">
         <v>82</v>
       </c>
-      <c r="C4" s="54" t="s">
+      <c r="C4" s="53" t="s">
         <v>168</v>
       </c>
-      <c r="D4" s="54" t="s">
+      <c r="D4" s="53" t="s">
         <v>169</v>
       </c>
     </row>
@@ -5208,10 +5622,10 @@
       <c r="B5" t="s">
         <v>83</v>
       </c>
-      <c r="C5" s="54" t="s">
+      <c r="C5" s="53" t="s">
         <v>170</v>
       </c>
-      <c r="D5" s="54" t="s">
+      <c r="D5" s="53" t="s">
         <v>171</v>
       </c>
     </row>
@@ -5222,10 +5636,10 @@
       <c r="B6" t="s">
         <v>84</v>
       </c>
-      <c r="C6" s="54" t="s">
+      <c r="C6" s="53" t="s">
         <v>172</v>
       </c>
-      <c r="D6" s="54" t="s">
+      <c r="D6" s="53" t="s">
         <v>173</v>
       </c>
     </row>
@@ -5236,10 +5650,10 @@
       <c r="B7" t="s">
         <v>85</v>
       </c>
-      <c r="C7" s="54" t="s">
+      <c r="C7" s="53" t="s">
         <v>174</v>
       </c>
-      <c r="D7" s="54" t="s">
+      <c r="D7" s="53" t="s">
         <v>175</v>
       </c>
     </row>
@@ -5250,10 +5664,10 @@
       <c r="B8" t="s">
         <v>86</v>
       </c>
-      <c r="C8" s="54" t="s">
+      <c r="C8" s="53" t="s">
         <v>176</v>
       </c>
-      <c r="D8" s="54" t="s">
+      <c r="D8" s="53" t="s">
         <v>177</v>
       </c>
     </row>
@@ -5264,10 +5678,10 @@
       <c r="B9" t="s">
         <v>80</v>
       </c>
-      <c r="C9" s="54" t="s">
+      <c r="C9" s="53" t="s">
         <v>178</v>
       </c>
-      <c r="D9" s="54" t="s">
+      <c r="D9" s="53" t="s">
         <v>179</v>
       </c>
     </row>
@@ -5278,10 +5692,10 @@
       <c r="B10" t="s">
         <v>81</v>
       </c>
-      <c r="C10" s="54" t="s">
+      <c r="C10" s="53" t="s">
         <v>180</v>
       </c>
-      <c r="D10" s="54" t="s">
+      <c r="D10" s="53" t="s">
         <v>181</v>
       </c>
     </row>
@@ -5292,10 +5706,10 @@
       <c r="B11" t="s">
         <v>82</v>
       </c>
-      <c r="C11" s="54" t="s">
+      <c r="C11" s="53" t="s">
         <v>182</v>
       </c>
-      <c r="D11" s="54" t="s">
+      <c r="D11" s="53" t="s">
         <v>183</v>
       </c>
     </row>
@@ -5306,10 +5720,10 @@
       <c r="B12" t="s">
         <v>83</v>
       </c>
-      <c r="C12" s="54" t="s">
+      <c r="C12" s="53" t="s">
         <v>184</v>
       </c>
-      <c r="D12" s="54" t="s">
+      <c r="D12" s="53" t="s">
         <v>185</v>
       </c>
     </row>
@@ -5320,10 +5734,10 @@
       <c r="B13" t="s">
         <v>84</v>
       </c>
-      <c r="C13" s="54" t="s">
+      <c r="C13" s="53" t="s">
         <v>186</v>
       </c>
-      <c r="D13" s="54" t="s">
+      <c r="D13" s="53" t="s">
         <v>187</v>
       </c>
     </row>
@@ -5334,10 +5748,10 @@
       <c r="B14" t="s">
         <v>85</v>
       </c>
-      <c r="C14" s="54" t="s">
+      <c r="C14" s="53" t="s">
         <v>188</v>
       </c>
-      <c r="D14" s="51" t="s">
+      <c r="D14" s="50" t="s">
         <v>189</v>
       </c>
     </row>
@@ -5348,10 +5762,10 @@
       <c r="B15" t="s">
         <v>86</v>
       </c>
-      <c r="C15" s="54" t="s">
+      <c r="C15" s="53" t="s">
         <v>190</v>
       </c>
-      <c r="D15" s="54" t="s">
+      <c r="D15" s="53" t="s">
         <v>191</v>
       </c>
     </row>
@@ -5362,10 +5776,10 @@
       <c r="B16" t="s">
         <v>87</v>
       </c>
-      <c r="C16" s="54" t="s">
+      <c r="C16" s="53" t="s">
         <v>192</v>
       </c>
-      <c r="D16" s="54" t="s">
+      <c r="D16" s="53" t="s">
         <v>193</v>
       </c>
     </row>
@@ -5376,10 +5790,10 @@
       <c r="B17" t="s">
         <v>88</v>
       </c>
-      <c r="C17" s="54" t="s">
+      <c r="C17" s="53" t="s">
         <v>194</v>
       </c>
-      <c r="D17" s="54" t="s">
+      <c r="D17" s="53" t="s">
         <v>195</v>
       </c>
     </row>
@@ -5390,10 +5804,10 @@
       <c r="B18" t="s">
         <v>89</v>
       </c>
-      <c r="C18" s="54" t="s">
+      <c r="C18" s="53" t="s">
         <v>196</v>
       </c>
-      <c r="D18" s="54" t="s">
+      <c r="D18" s="53" t="s">
         <v>197</v>
       </c>
     </row>
@@ -5404,10 +5818,10 @@
       <c r="B19" t="s">
         <v>80</v>
       </c>
-      <c r="C19" s="54" t="s">
+      <c r="C19" s="53" t="s">
         <v>229</v>
       </c>
-      <c r="D19" s="54" t="s">
+      <c r="D19" s="53" t="s">
         <v>230</v>
       </c>
     </row>
@@ -5418,10 +5832,10 @@
       <c r="B20" t="s">
         <v>81</v>
       </c>
-      <c r="C20" s="54" t="s">
+      <c r="C20" s="53" t="s">
         <v>231</v>
       </c>
-      <c r="D20" s="54" t="s">
+      <c r="D20" s="53" t="s">
         <v>232</v>
       </c>
     </row>
@@ -5432,10 +5846,10 @@
       <c r="B21" t="s">
         <v>82</v>
       </c>
-      <c r="C21" s="54" t="s">
+      <c r="C21" s="53" t="s">
         <v>233</v>
       </c>
-      <c r="D21" s="54" t="s">
+      <c r="D21" s="53" t="s">
         <v>234</v>
       </c>
     </row>
@@ -5449,7 +5863,7 @@
       <c r="C22" t="s">
         <v>235</v>
       </c>
-      <c r="D22" s="54" t="s">
+      <c r="D22" s="53" t="s">
         <v>236</v>
       </c>
     </row>
@@ -5460,10 +5874,10 @@
       <c r="B23" t="s">
         <v>84</v>
       </c>
-      <c r="C23" s="54" t="s">
+      <c r="C23" s="53" t="s">
         <v>237</v>
       </c>
-      <c r="D23" s="54" t="s">
+      <c r="D23" s="53" t="s">
         <v>238</v>
       </c>
     </row>
@@ -5474,10 +5888,10 @@
       <c r="B24" t="s">
         <v>85</v>
       </c>
-      <c r="C24" s="54" t="s">
+      <c r="C24" s="53" t="s">
         <v>239</v>
       </c>
-      <c r="D24" s="54" t="s">
+      <c r="D24" s="53" t="s">
         <v>240</v>
       </c>
     </row>
@@ -5491,8 +5905,103 @@
       <c r="C25" t="s">
         <v>241</v>
       </c>
-      <c r="D25" s="54" t="s">
+      <c r="D25" s="53" t="s">
         <v>242</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="39.6" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
+        <v>80</v>
+      </c>
+      <c r="C26" s="53" t="s">
+        <v>288</v>
+      </c>
+      <c r="D26" s="53" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="39.6" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>248</v>
+      </c>
+      <c r="B27" t="s">
+        <v>81</v>
+      </c>
+      <c r="C27" s="53" t="s">
+        <v>290</v>
+      </c>
+      <c r="D27" s="53" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="39.6" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>248</v>
+      </c>
+      <c r="B28" t="s">
+        <v>82</v>
+      </c>
+      <c r="C28" s="53" t="s">
+        <v>292</v>
+      </c>
+      <c r="D28" s="53" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>248</v>
+      </c>
+      <c r="B29" t="s">
+        <v>83</v>
+      </c>
+      <c r="C29" s="53" t="s">
+        <v>294</v>
+      </c>
+      <c r="D29" s="53" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="39.6" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>248</v>
+      </c>
+      <c r="B30" t="s">
+        <v>84</v>
+      </c>
+      <c r="C30" s="53" t="s">
+        <v>296</v>
+      </c>
+      <c r="D30" s="53" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>248</v>
+      </c>
+      <c r="B31" t="s">
+        <v>85</v>
+      </c>
+      <c r="C31" t="s">
+        <v>298</v>
+      </c>
+      <c r="D31" s="53" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>248</v>
+      </c>
+      <c r="B32" t="s">
+        <v>86</v>
+      </c>
+      <c r="C32" s="53" t="s">
+        <v>300</v>
+      </c>
+      <c r="D32" s="50" t="s">
+        <v>301</v>
       </c>
     </row>
   </sheetData>
@@ -5520,31 +6029,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="3" customFormat="1" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="39" t="s">
+      <c r="B1" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="39" t="s">
+      <c r="C1" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="39" t="s">
+      <c r="D1" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="39" t="s">
+      <c r="E1" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="39" t="s">
+      <c r="F1" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="39" t="s">
+      <c r="G1" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="39" t="s">
+      <c r="H1" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="39" t="s">
+      <c r="I1" s="38" t="s">
         <v>8</v>
       </c>
     </row>
@@ -5555,25 +6064,25 @@
       <c r="B2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="60">
+      <c r="C2" s="59">
         <v>46260</v>
       </c>
-      <c r="D2" s="60">
+      <c r="D2" s="59">
         <v>46268</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="54" t="s">
+      <c r="F2" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="54" t="s">
+      <c r="G2" s="53" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="54" t="s">
+      <c r="H2" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="54" t="s">
+      <c r="I2" s="53" t="s">
         <v>14</v>
       </c>
     </row>
@@ -5584,25 +6093,25 @@
       <c r="B3" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="60">
+      <c r="C3" s="59">
         <v>46269</v>
       </c>
-      <c r="D3" s="60">
+      <c r="D3" s="59">
         <v>46278</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="54" t="s">
+      <c r="F3" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="54" t="s">
+      <c r="G3" s="53" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="54" t="s">
+      <c r="H3" s="53" t="s">
         <v>18</v>
       </c>
-      <c r="I3" s="54" t="s">
+      <c r="I3" s="53" t="s">
         <v>19</v>
       </c>
     </row>
@@ -5613,40 +6122,56 @@
       <c r="B4" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="C4" s="61">
+      <c r="C4" s="60">
         <v>46279</v>
       </c>
-      <c r="D4" s="73">
+      <c r="D4" s="61">
         <v>46289</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="54" t="s">
+      <c r="F4" s="53" t="s">
         <v>243</v>
       </c>
       <c r="G4" s="8" t="s">
         <v>244</v>
       </c>
-      <c r="H4" s="54" t="s">
+      <c r="H4" s="53" t="s">
         <v>245</v>
       </c>
-      <c r="I4" s="54" t="s">
+      <c r="I4" s="53" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="92.4" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
         <v>4</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="11"/>
+      <c r="B5" t="s">
+        <v>248</v>
+      </c>
+      <c r="C5" s="61">
+        <v>46290</v>
+      </c>
+      <c r="D5" s="61">
+        <v>46299</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="53" t="s">
+        <v>302</v>
+      </c>
+      <c r="G5" s="53" t="s">
+        <v>303</v>
+      </c>
+      <c r="H5" s="53" t="s">
+        <v>304</v>
+      </c>
+      <c r="I5" s="53" t="s">
+        <v>305</v>
+      </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
@@ -5655,11 +6180,11 @@
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
-      <c r="E6" s="11"/>
+      <c r="E6" s="10"/>
       <c r="F6" s="7"/>
       <c r="G6" s="9"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
@@ -5668,11 +6193,11 @@
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="11"/>
+      <c r="E7" s="10"/>
       <c r="F7" s="7"/>
       <c r="G7" s="8"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="11"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
@@ -5681,11 +6206,11 @@
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="11"/>
+      <c r="E8" s="10"/>
       <c r="F8" s="7"/>
       <c r="G8" s="9"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="10"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="7"/>
